--- a/Trade-Surveillance-Data-Schema.xlsx
+++ b/Trade-Surveillance-Data-Schema.xlsx
@@ -216,9 +216,7 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment/>
-    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="7" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -630,8 +628,8 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="T_FACT_TRADE" displayName="T_FACT_TRADE" ref="A5:K56" headerRowCount="1">
-  <autoFilter ref="A5:K56"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="T_FACT_TRADE" displayName="T_FACT_TRADE" ref="A5:K58" headerRowCount="1">
+  <autoFilter ref="A5:K58"/>
   <tableColumns count="11">
     <tableColumn id="1" name="#"/>
     <tableColumn id="2" name="Field name"/>
@@ -854,7 +852,7 @@
 </file>
 
 <file path=xl/tables/table30.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="30" name="OpenGaps" displayName="OpenGaps" ref="A4:E16" headerRowCount="1">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="30" name="OpenGaps" displayName="OpenGaps" ref="A4:E17" headerRowCount="1">
   <autoFilter ref="A4:E16"/>
   <tableColumns count="5">
     <tableColumn id="1" name="Gap"/>
@@ -1310,7 +1308,6 @@
         </is>
       </c>
     </row>
-    <row r="5"/>
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
         <is>
@@ -1323,7 +1320,6 @@
         </is>
       </c>
     </row>
-    <row r="7"/>
     <row r="8">
       <c r="A8" s="3" t="inlineStr">
         <is>
@@ -1336,7 +1332,6 @@
         </is>
       </c>
     </row>
-    <row r="9"/>
     <row r="10">
       <c r="A10" s="3" t="inlineStr">
         <is>
@@ -1356,7 +1351,6 @@
         </is>
       </c>
     </row>
-    <row r="11"/>
     <row r="12">
       <c r="A12" s="3" t="inlineStr">
         <is>
@@ -1378,7 +1372,6 @@
         </is>
       </c>
     </row>
-    <row r="13"/>
     <row r="14">
       <c r="A14" s="3" t="inlineStr">
         <is>
@@ -1394,7 +1387,6 @@
         </is>
       </c>
     </row>
-    <row r="15"/>
     <row r="16">
       <c r="A16" s="5" t="inlineStr">
         <is>
@@ -1410,7 +1402,6 @@
         </is>
       </c>
     </row>
-    <row r="17"/>
     <row r="18">
       <c r="A18" s="3" t="inlineStr">
         <is>
@@ -1423,7 +1414,6 @@
         </is>
       </c>
     </row>
-    <row r="19"/>
     <row r="20">
       <c r="A20" s="3" t="inlineStr">
         <is>
@@ -1436,7 +1426,6 @@
         </is>
       </c>
     </row>
-    <row r="21"/>
     <row r="22">
       <c r="A22" s="3" t="inlineStr">
         <is>
@@ -1449,7 +1438,6 @@
         </is>
       </c>
     </row>
-    <row r="23"/>
     <row r="24">
       <c r="A24" s="3" t="inlineStr">
         <is>
@@ -1498,7 +1486,7 @@
       </c>
     </row>
     <row r="2" ht="14" customHeight="1">
-      <c r="A2" s="8" t="inlineStr">
+      <c r="A2" s="42" t="inlineStr">
         <is>
           <t>Fact  ·  Grain: one row per deal  ·  PK: trade_id</t>
         </is>
@@ -1937,7 +1925,7 @@
       </c>
     </row>
     <row r="2" ht="14" customHeight="1">
-      <c r="A2" s="8" t="inlineStr">
+      <c r="A2" s="42" t="inlineStr">
         <is>
           <t>Fact — output  ·  Grain: one row per alert  ·  PK: alert_id</t>
         </is>
@@ -3586,7 +3574,7 @@
       </c>
     </row>
     <row r="2" ht="14" customHeight="1">
-      <c r="A2" s="8" t="inlineStr">
+      <c r="A2" s="42" t="inlineStr">
         <is>
           <t>Bridge  ·  Grain: one row per alert-to-deal citation  ·  PK: alert_id + trade_id</t>
         </is>
@@ -3915,7 +3903,7 @@
       </c>
     </row>
     <row r="2" ht="14" customHeight="1">
-      <c r="A2" s="8" t="inlineStr">
+      <c r="A2" s="42" t="inlineStr">
         <is>
           <t>Fact — output  ·  Grain: one row per evidence line on an alert  ·  PK: alert_id + line_no</t>
         </is>
@@ -4354,7 +4342,7 @@
       </c>
     </row>
     <row r="2" ht="14" customHeight="1">
-      <c r="A2" s="8" t="inlineStr">
+      <c r="A2" s="42" t="inlineStr">
         <is>
           <t>Fact — audit  ·  Grain: one row per workflow event on an alert  ·  PK: alert_id + event_seq</t>
         </is>
@@ -4848,7 +4836,7 @@
       </c>
     </row>
     <row r="2" ht="14" customHeight="1">
-      <c r="A2" s="8" t="inlineStr">
+      <c r="A2" s="42" t="inlineStr">
         <is>
           <t>Dimension — type 2  ·  Grain: one row per trader per validity window  ·  PK: trader_id + effective_from</t>
         </is>
@@ -5947,7 +5935,7 @@
       </c>
     </row>
     <row r="2" ht="14" customHeight="1">
-      <c r="A2" s="8" t="inlineStr">
+      <c r="A2" s="42" t="inlineStr">
         <is>
           <t>Dimension — type 2  ·  Grain: one row per desk per validity window  ·  PK: desk_id + effective_from</t>
         </is>
@@ -6661,7 +6649,7 @@
       </c>
     </row>
     <row r="2" ht="14" customHeight="1">
-      <c r="A2" s="8" t="inlineStr">
+      <c r="A2" s="42" t="inlineStr">
         <is>
           <t>Dimension  ·  Grain: one row per instrument  ·  PK: instrument_id</t>
         </is>
@@ -7485,7 +7473,7 @@
       </c>
     </row>
     <row r="2" ht="14" customHeight="1">
-      <c r="A2" s="8" t="inlineStr">
+      <c r="A2" s="42" t="inlineStr">
         <is>
           <t>Dimension  ·  Grain: one row per product  ·  PK: product</t>
         </is>
@@ -8034,7 +8022,7 @@
       </c>
     </row>
     <row r="2" ht="14" customHeight="1">
-      <c r="A2" s="8" t="inlineStr">
+      <c r="A2" s="42" t="inlineStr">
         <is>
           <t>Dimension  ·  Grain: one row per legal entity  ·  PK: counterparty_id (LEI)</t>
         </is>
@@ -8637,7 +8625,7 @@
       </c>
     </row>
     <row r="2" ht="14" customHeight="1">
-      <c r="A2" s="8" t="inlineStr">
+      <c r="A2" s="42" t="inlineStr">
         <is>
           <t>24 tables. Build in priority order — Priority 1 tables are required before the dashboard will render.</t>
         </is>
@@ -8723,7 +8711,7 @@
       </c>
       <c r="F5" s="10" t="inlineStr">
         <is>
-          <t>Trade capture (booking systems), enriched with market data and FX rates</t>
+          <t>Trade capture (booking systems), enriched with market data, FX rates and — for the two revenue fields — revenue attribution</t>
         </is>
       </c>
       <c r="G5" s="10" t="inlineStr">
@@ -9982,7 +9970,7 @@
       </c>
     </row>
     <row r="2" ht="14" customHeight="1">
-      <c r="A2" s="8" t="inlineStr">
+      <c r="A2" s="42" t="inlineStr">
         <is>
           <t>Reference — dated  ·  Grain: one row per listed entity per validity window  ·  PK: list_type + entry_id + valid_from</t>
         </is>
@@ -10531,7 +10519,7 @@
       </c>
     </row>
     <row r="2" ht="14" customHeight="1">
-      <c r="A2" s="8" t="inlineStr">
+      <c r="A2" s="42" t="inlineStr">
         <is>
           <t>Reference — type 2  ·  Grain: one row per SSI per validity window  ·  PK: ssi_id + valid_from</t>
         </is>
@@ -11135,7 +11123,7 @@
       </c>
     </row>
     <row r="2" ht="14" customHeight="1">
-      <c r="A2" s="8" t="inlineStr">
+      <c r="A2" s="42" t="inlineStr">
         <is>
           <t>Reference  ·  Grain: one row per date per settlement centre  ·  PK: calendar_date + centre</t>
         </is>
@@ -11629,7 +11617,7 @@
       </c>
     </row>
     <row r="2" ht="14" customHeight="1">
-      <c r="A2" s="8" t="inlineStr">
+      <c r="A2" s="42" t="inlineStr">
         <is>
           <t>Reference  ·  Grain: one row per leave period per staff member  ·  PK: trader_id + leave_start</t>
         </is>
@@ -12013,7 +12001,7 @@
       </c>
     </row>
     <row r="2" ht="14" customHeight="1">
-      <c r="A2" s="8" t="inlineStr">
+      <c r="A2" s="42" t="inlineStr">
         <is>
           <t>Aggregate — derived  ·  Grain: one row per trader per as-of date  ·  PK: trader_id + as_of_date</t>
         </is>
@@ -13827,7 +13815,7 @@
       </c>
     </row>
     <row r="2" ht="14" customHeight="1">
-      <c r="A2" s="8" t="inlineStr">
+      <c r="A2" s="42" t="inlineStr">
         <is>
           <t>Reference  ·  Grain: one row per typology  ·  PK: rule_id</t>
         </is>
@@ -14541,7 +14529,7 @@
       </c>
     </row>
     <row r="2" ht="14" customHeight="1">
-      <c r="A2" s="8" t="inlineStr">
+      <c r="A2" s="42" t="inlineStr">
         <is>
           <t>Reference  ·  Grain: one row per data element the rule library consumes  ·  PK: element_code</t>
         </is>
@@ -15029,7 +15017,7 @@
       </c>
     </row>
     <row r="2" ht="14" customHeight="1">
-      <c r="A2" s="8" t="inlineStr">
+      <c r="A2" s="42" t="inlineStr">
         <is>
           <t>Complete valid-value sets extracted from the working dashboard. Any value outside these lists must be normalised upstream, not handled in the UI.</t>
         </is>
@@ -17816,7 +17804,7 @@
       </c>
     </row>
     <row r="2" ht="14" customHeight="1">
-      <c r="A2" s="8" t="inlineStr">
+      <c r="A2" s="42" t="inlineStr">
         <is>
           <t>M = mandatory   ·   C = conditional (see note)   ·   n/a = not applicable, leave null. Percentages are the observed fill rate in the prototype dataset.</t>
         </is>
@@ -19108,7 +19096,7 @@
       </c>
     </row>
     <row r="2" ht="14" customHeight="1">
-      <c r="A2" s="8" t="inlineStr">
+      <c r="A2" s="42" t="inlineStr">
         <is>
           <t>Sorted by the number of rules that depend on each element. Source the top of this list first: it unlocks the most rules per unit of effort.</t>
         </is>
@@ -21266,7 +21254,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K56"/>
+  <dimension ref="A1:K58"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -21290,7 +21278,7 @@
       </c>
     </row>
     <row r="2" ht="14" customHeight="1">
-      <c r="A2" s="8" t="inlineStr">
+      <c r="A2" s="42" t="inlineStr">
         <is>
           <t>Fact — core  ·  Grain: one row per executed deal version  ·  PK: trade_id + trade_version</t>
         </is>
@@ -24006,22 +23994,22 @@
       </c>
       <c r="B54" s="19" t="inlineStr">
         <is>
-          <t>credit_rating</t>
+          <t>client_revenue_usd</t>
         </is>
       </c>
       <c r="C54" s="10" t="inlineStr">
         <is>
-          <t>Issuer rating. Bonds and credit derivatives only.</t>
+          <t>Dealing revenue earned on the ticket — the spread the desk captured on the deal, before any result from holding the risk it took on. USD thousands.</t>
         </is>
       </c>
       <c r="D54" s="10" t="inlineStr">
         <is>
-          <t>VARCHAR(6)</t>
+          <t>DECIMAL(18,3)</t>
         </is>
       </c>
       <c r="E54" s="10" t="inlineStr">
         <is>
-          <t>S&amp;P-style. Observed 4 chars.</t>
+          <t>Unsigned. Zero for internal bookings and transfers.</t>
         </is>
       </c>
       <c r="F54" s="15" t="inlineStr">
@@ -24036,22 +24024,22 @@
       </c>
       <c r="H54" s="10" t="inlineStr">
         <is>
-          <t>AAA .. D</t>
+          <t>0 .. 95 observed in the prototype; 0 for internal transfers</t>
         </is>
       </c>
       <c r="I54" s="10" t="inlineStr">
         <is>
-          <t>BBB-</t>
+          <t>0.214</t>
         </is>
       </c>
       <c r="J54" s="10" t="inlineStr">
         <is>
-          <t>Reference data</t>
+          <t>Revenue attribution / product control</t>
         </is>
       </c>
       <c r="K54" s="10" t="inlineStr">
         <is>
-          <t>Populated for 20% of Bonds and 64% of Credit Derivatives rows in the prototype; null for everything else.</t>
+          <t>Feeds the P&amp;L view of the Trade Activity tab (payload key clientRevenue). Not the same number as deal_pnl_usd, which values the deal's price deviation for the surveillance rules — this one is what the desk charged the client. Conditional: supply it with total_revenue_usd or omit both, in which case the P&amp;L view reads zero and no other panel is affected.</t>
         </is>
       </c>
     </row>
@@ -24061,27 +24049,27 @@
       </c>
       <c r="B55" s="22" t="inlineStr">
         <is>
-          <t>source_system</t>
+          <t>total_revenue_usd</t>
         </is>
       </c>
       <c r="C55" s="13" t="inlineStr">
         <is>
-          <t>System the record was extracted from.</t>
+          <t>Client revenue plus the result of holding the risk the deal took on. The figure the Trade Activity P&amp;L view sums. USD thousands.</t>
         </is>
       </c>
       <c r="D55" s="13" t="inlineStr">
         <is>
-          <t>VARCHAR(30)</t>
+          <t>DECIMAL(18,3)</t>
         </is>
       </c>
       <c r="E55" s="13" t="inlineStr">
         <is>
-          <t>Free text.</t>
+          <t>Signed — an individual ticket can lose money.</t>
         </is>
       </c>
       <c r="F55" s="12" t="inlineStr">
         <is>
-          <t>Mandatory</t>
+          <t>Conditional</t>
         </is>
       </c>
       <c r="G55" s="13" t="inlineStr">
@@ -24091,22 +24079,22 @@
       </c>
       <c r="H55" s="13" t="inlineStr">
         <is>
-          <t>Your booking systems</t>
+          <t>-8 .. +131 observed; roughly one ticket in ten negative</t>
         </is>
       </c>
       <c r="I55" s="13" t="inlineStr">
         <is>
-          <t>MUREX-SG</t>
+          <t>0.347</t>
         </is>
       </c>
       <c r="J55" s="13" t="inlineStr">
         <is>
-          <t>Ingestion</t>
+          <t>Revenue attribution / product control</t>
         </is>
       </c>
       <c r="K55" s="13" t="inlineStr">
         <is>
-          <t>Lineage / reconciliation.</t>
+          <t>Payload key revenue. Must reconcile to the revenue the desk reports for the period: if it does not, the dashboard and the P&amp;L report will disagree in front of the same reader. The difference between this and client_revenue_usd is what the view attributes to risk-taking, so supply both or neither.</t>
         </is>
       </c>
     </row>
@@ -24116,50 +24104,160 @@
       </c>
       <c r="B56" s="19" t="inlineStr">
         <is>
+          <t>credit_rating</t>
+        </is>
+      </c>
+      <c r="C56" s="10" t="inlineStr">
+        <is>
+          <t>Issuer rating. Bonds and credit derivatives only.</t>
+        </is>
+      </c>
+      <c r="D56" s="10" t="inlineStr">
+        <is>
+          <t>VARCHAR(6)</t>
+        </is>
+      </c>
+      <c r="E56" s="10" t="inlineStr">
+        <is>
+          <t>S&amp;P-style. Observed 4 chars.</t>
+        </is>
+      </c>
+      <c r="F56" s="15" t="inlineStr">
+        <is>
+          <t>Conditional</t>
+        </is>
+      </c>
+      <c r="G56" s="10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H56" s="10" t="inlineStr">
+        <is>
+          <t>AAA .. D</t>
+        </is>
+      </c>
+      <c r="I56" s="10" t="inlineStr">
+        <is>
+          <t>BBB-</t>
+        </is>
+      </c>
+      <c r="J56" s="10" t="inlineStr">
+        <is>
+          <t>Reference data</t>
+        </is>
+      </c>
+      <c r="K56" s="10" t="inlineStr">
+        <is>
+          <t>Populated for 20% of Bonds and 64% of Credit Derivatives rows in the prototype; null for everything else.</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="21" t="n">
+        <v>52</v>
+      </c>
+      <c r="B57" s="22" t="inlineStr">
+        <is>
+          <t>source_system</t>
+        </is>
+      </c>
+      <c r="C57" s="13" t="inlineStr">
+        <is>
+          <t>System the record was extracted from.</t>
+        </is>
+      </c>
+      <c r="D57" s="13" t="inlineStr">
+        <is>
+          <t>VARCHAR(30)</t>
+        </is>
+      </c>
+      <c r="E57" s="13" t="inlineStr">
+        <is>
+          <t>Free text.</t>
+        </is>
+      </c>
+      <c r="F57" s="12" t="inlineStr">
+        <is>
+          <t>Mandatory</t>
+        </is>
+      </c>
+      <c r="G57" s="13" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H57" s="13" t="inlineStr">
+        <is>
+          <t>Your booking systems</t>
+        </is>
+      </c>
+      <c r="I57" s="13" t="inlineStr">
+        <is>
+          <t>MUREX-SG</t>
+        </is>
+      </c>
+      <c r="J57" s="13" t="inlineStr">
+        <is>
+          <t>Ingestion</t>
+        </is>
+      </c>
+      <c r="K57" s="13" t="inlineStr">
+        <is>
+          <t>Lineage / reconciliation.</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="18" t="n">
+        <v>53</v>
+      </c>
+      <c r="B58" s="19" t="inlineStr">
+        <is>
           <t>ingested_at</t>
         </is>
       </c>
-      <c r="C56" s="10" t="inlineStr">
+      <c r="C58" s="10" t="inlineStr">
         <is>
           <t>Warehouse load timestamp.</t>
         </is>
       </c>
-      <c r="D56" s="10" t="inlineStr">
+      <c r="D58" s="10" t="inlineStr">
         <is>
           <t>TIMESTAMP(6) WITH TIME ZONE</t>
         </is>
       </c>
-      <c r="E56" s="10" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F56" s="12" t="inlineStr">
+      <c r="E58" s="10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F58" s="15" t="inlineStr">
         <is>
           <t>Mandatory</t>
         </is>
       </c>
-      <c r="G56" s="10" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H56" s="10" t="inlineStr">
+      <c r="G58" s="10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H58" s="10" t="inlineStr">
         <is>
           <t>Any</t>
         </is>
       </c>
-      <c r="I56" s="10" t="inlineStr">
+      <c r="I58" s="10" t="inlineStr">
         <is>
           <t>2025-08-05T02:15:00Z</t>
         </is>
       </c>
-      <c r="J56" s="10" t="inlineStr">
+      <c r="J58" s="10" t="inlineStr">
         <is>
           <t>Ingestion</t>
         </is>
       </c>
-      <c r="K56" s="10" t="inlineStr">
+      <c r="K58" s="10" t="inlineStr">
         <is>
           <t>Operational — not shown in the UI.</t>
         </is>
@@ -24201,7 +24299,7 @@
       </c>
     </row>
     <row r="2" ht="14" customHeight="1">
-      <c r="A2" s="8" t="inlineStr">
+      <c r="A2" s="42" t="inlineStr">
         <is>
           <t>'Baseline used' names what the rule measures against. 41 of the 50 measure against a reference specific to the trader, instrument or product rather than a bank-wide fixed number; the other 9 test against a static list or tolerance.</t>
         </is>
@@ -26341,7 +26439,7 @@
       </c>
     </row>
     <row r="2" ht="14" customHeight="1">
-      <c r="A2" s="8" t="inlineStr">
+      <c r="A2" s="42" t="inlineStr">
         <is>
           <t>X marks a dependency. Read down a column to see which rules a missing element disables.</t>
         </is>
@@ -32452,9 +32550,9 @@
       </c>
     </row>
     <row r="2" ht="14" customHeight="1">
-      <c r="A2" s="8" t="inlineStr">
-        <is>
-          <t>All 31 panels across the 8 dashboard tabs. If a panel is not needed, the tables in its row may still be required by others — check '01 Table Index' before dropping anything.</t>
+      <c r="A2" s="42" t="inlineStr">
+        <is>
+          <t>All 31 panels across the 8 dashboard tabs. If a panel is not needed, the tables in its row may still be required by others — check '01 Table Index' before dropping anything. The eleven Trade Activity panels are drawn in a measure the reader chooses — deals and notional, or P&amp;L and margin — so each one has two readings of the same cut and needs the revenue fields as well as the volume ones.</t>
         </is>
       </c>
     </row>
@@ -32938,7 +33036,7 @@
       </c>
       <c r="D15" s="10" t="inlineStr">
         <is>
-          <t>Count of deals and notional</t>
+          <t>Count of deals and notional, or P&amp;L</t>
         </is>
       </c>
       <c r="E15" s="10" t="inlineStr">
@@ -32953,7 +33051,7 @@
       </c>
       <c r="G15" s="10" t="inlineStr">
         <is>
-          <t>trade_date, notional_usd</t>
+          <t>trade_date, notional_usd, total_revenue_usd</t>
         </is>
       </c>
       <c r="H15" s="10" t="inlineStr">
@@ -32980,7 +33078,7 @@
       </c>
       <c r="D16" s="13" t="inlineStr">
         <is>
-          <t>Notional</t>
+          <t>Notional, or share of P&amp;L</t>
         </is>
       </c>
       <c r="E16" s="13" t="inlineStr">
@@ -32995,7 +33093,7 @@
       </c>
       <c r="G16" s="13" t="inlineStr">
         <is>
-          <t>asset_class, notional_usd</t>
+          <t>asset_class, notional_usd, total_revenue_usd</t>
         </is>
       </c>
       <c r="H16" s="13" t="inlineStr">
@@ -33022,7 +33120,7 @@
       </c>
       <c r="D17" s="10" t="inlineStr">
         <is>
-          <t>Count of deals</t>
+          <t>Count of deals, or share of P&amp;L</t>
         </is>
       </c>
       <c r="E17" s="10" t="inlineStr">
@@ -33037,7 +33135,7 @@
       </c>
       <c r="G17" s="10" t="inlineStr">
         <is>
-          <t>channel</t>
+          <t>channel, total_revenue_usd</t>
         </is>
       </c>
       <c r="H17" s="10" t="inlineStr">
@@ -33064,7 +33162,7 @@
       </c>
       <c r="D18" s="13" t="inlineStr">
         <is>
-          <t>Count of deals</t>
+          <t>Count of deals, or P&amp;L</t>
         </is>
       </c>
       <c r="E18" s="13" t="inlineStr">
@@ -33079,7 +33177,7 @@
       </c>
       <c r="G18" s="13" t="inlineStr">
         <is>
-          <t>product</t>
+          <t>product, total_revenue_usd</t>
         </is>
       </c>
       <c r="H18" s="13" t="inlineStr">
@@ -33106,7 +33204,7 @@
       </c>
       <c r="D19" s="10" t="inlineStr">
         <is>
-          <t>Notional</t>
+          <t>Notional, or P&amp;L per $1m traded (margin)</t>
         </is>
       </c>
       <c r="E19" s="10" t="inlineStr">
@@ -33121,7 +33219,7 @@
       </c>
       <c r="G19" s="10" t="inlineStr">
         <is>
-          <t>product, notional_usd</t>
+          <t>product, notional_usd, total_revenue_usd</t>
         </is>
       </c>
       <c r="H19" s="10" t="inlineStr">
@@ -33148,7 +33246,7 @@
       </c>
       <c r="D20" s="13" t="inlineStr">
         <is>
-          <t>Count of deals</t>
+          <t>Count of deals, or P&amp;L</t>
         </is>
       </c>
       <c r="E20" s="13" t="inlineStr">
@@ -33163,7 +33261,7 @@
       </c>
       <c r="G20" s="13" t="inlineStr">
         <is>
-          <t>counterparty_id, counterparty_name</t>
+          <t>counterparty_id, counterparty_name, total_revenue_usd</t>
         </is>
       </c>
       <c r="H20" s="13" t="inlineStr">
@@ -33190,7 +33288,7 @@
       </c>
       <c r="D21" s="10" t="inlineStr">
         <is>
-          <t>Notional</t>
+          <t>Notional, or P&amp;L per $1m traded (margin)</t>
         </is>
       </c>
       <c r="E21" s="10" t="inlineStr">
@@ -33205,7 +33303,7 @@
       </c>
       <c r="G21" s="10" t="inlineStr">
         <is>
-          <t>counterparty_id, notional_usd</t>
+          <t>counterparty_id, notional_usd, total_revenue_usd</t>
         </is>
       </c>
       <c r="H21" s="10" t="inlineStr">
@@ -33232,7 +33330,7 @@
       </c>
       <c r="D22" s="13" t="inlineStr">
         <is>
-          <t>Count of deals</t>
+          <t>Count of deals, or P&amp;L</t>
         </is>
       </c>
       <c r="E22" s="13" t="inlineStr">
@@ -33247,7 +33345,7 @@
       </c>
       <c r="G22" s="13" t="inlineStr">
         <is>
-          <t>exec_timestamp, timezone</t>
+          <t>exec_timestamp, timezone, total_revenue_usd</t>
         </is>
       </c>
       <c r="H22" s="13" t="inlineStr">
@@ -33274,7 +33372,7 @@
       </c>
       <c r="D23" s="10" t="inlineStr">
         <is>
-          <t>Count of deals</t>
+          <t>Count of deals, or P&amp;L</t>
         </is>
       </c>
       <c r="E23" s="10" t="inlineStr">
@@ -33289,7 +33387,7 @@
       </c>
       <c r="G23" s="10" t="inlineStr">
         <is>
-          <t>size_band, notional_usd</t>
+          <t>size_band, notional_usd, total_revenue_usd</t>
         </is>
       </c>
       <c r="H23" s="10" t="inlineStr">
@@ -33316,7 +33414,7 @@
       </c>
       <c r="D24" s="13" t="inlineStr">
         <is>
-          <t>Count of deals</t>
+          <t>Count of deals, or P&amp;L</t>
         </is>
       </c>
       <c r="E24" s="13" t="inlineStr">
@@ -33331,7 +33429,7 @@
       </c>
       <c r="G24" s="13" t="inlineStr">
         <is>
-          <t>tenor_band, tenor_years</t>
+          <t>tenor_band, tenor_years, total_revenue_usd</t>
         </is>
       </c>
       <c r="H24" s="13" t="inlineStr">
@@ -33358,7 +33456,7 @@
       </c>
       <c r="D25" s="10" t="inlineStr">
         <is>
-          <t>Count of deals or notional</t>
+          <t>Count of deals, notional, tenor spread, or P&amp;L</t>
         </is>
       </c>
       <c r="E25" s="10" t="inlineStr">
@@ -33373,7 +33471,7 @@
       </c>
       <c r="G25" s="10" t="inlineStr">
         <is>
-          <t>trader_id, trader_name, notional_usd</t>
+          <t>trader_id, trader_name, notional_usd, total_revenue_usd</t>
         </is>
       </c>
       <c r="H25" s="10" t="inlineStr">
@@ -33877,7 +33975,7 @@
       </c>
     </row>
     <row r="2" ht="14" customHeight="1">
-      <c r="A2" s="8" t="inlineStr">
+      <c r="A2" s="42" t="inlineStr">
         <is>
           <t>28 controls. 'Action on failure' is the required behaviour, not a suggestion — silently defaulting a failed control produces findings against individuals that cannot be defended.</t>
         </is>
@@ -34681,7 +34779,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E16"/>
+  <dimension ref="A1:E17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="36" customWidth="1" min="1" max="1"/>
@@ -34699,7 +34797,7 @@
       </c>
     </row>
     <row r="2" ht="14" customHeight="1">
-      <c r="A2" s="8" t="inlineStr">
+      <c r="A2" s="42" t="inlineStr">
         <is>
           <t>These are the data requirements most often missing, undated, or owned by nobody. Resolve them during discovery, before the build is scoped.</t>
         </is>
@@ -35053,6 +35151,33 @@
       <c r="E16" s="13" t="inlineStr">
         <is>
           <t>Agree and publish the weighting; store the component inputs alongside the score.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="49" t="inlineStr">
+        <is>
+          <t>Deal-level revenue attribution</t>
+        </is>
+      </c>
+      <c r="B17" s="21" t="inlineStr">
+        <is>
+          <t>FACT_TRADE.client_revenue_usd, FACT_TRADE.total_revenue_usd</t>
+        </is>
+      </c>
+      <c r="C17" s="13" t="inlineStr">
+        <is>
+          <t>No rule. The P&amp;L view of all eleven Trade Activity panels.</t>
+        </is>
+      </c>
+      <c r="D17" s="13" t="inlineStr">
+        <is>
+          <t>Revenue is usually attributed at desk and book level for the P&amp;L report, not carried on the ticket, and the split between what was charged the client and what came from holding the risk often exists only inside product control's own model. A front-office estimate is not a substitute: the dashboard will be read next to the official P&amp;L and the two must agree.</t>
+        </is>
+      </c>
+      <c r="E17" s="13" t="inlineStr">
+        <is>
+          <t>Agree with product control whether per-deal attribution can be published, and at what lag. If it cannot, omit both fields — the P&amp;L toggle then reads zero and every other panel is unaffected — rather than filling them with an estimate.</t>
         </is>
       </c>
     </row>
@@ -35095,7 +35220,7 @@
       </c>
     </row>
     <row r="2" ht="14" customHeight="1">
-      <c r="A2" s="8" t="inlineStr">
+      <c r="A2" s="42" t="inlineStr">
         <is>
           <t>Fact — audit  ·  Grain: one row per amendment or cancellation event  ·  PK: trade_id + amend_seq</t>
         </is>
@@ -35699,7 +35824,7 @@
       </c>
     </row>
     <row r="2" ht="14" customHeight="1">
-      <c r="A2" s="8" t="inlineStr">
+      <c r="A2" s="42" t="inlineStr">
         <is>
           <t>Fact  ·  Grain: one row per order version  ·  PK: order_id + order_version</t>
         </is>
@@ -36523,7 +36648,7 @@
       </c>
     </row>
     <row r="2" ht="14" customHeight="1">
-      <c r="A2" s="8" t="inlineStr">
+      <c r="A2" s="42" t="inlineStr">
         <is>
           <t>Fact — market data  ·  Grain: one row per instrument per quote timestamp  ·  PK: instrument_id + quote_timestamp</t>
         </is>
@@ -37127,7 +37252,7 @@
       </c>
     </row>
     <row r="2" ht="14" customHeight="1">
-      <c r="A2" s="8" t="inlineStr">
+      <c r="A2" s="42" t="inlineStr">
         <is>
           <t>Fact  ·  Grain: one row per trader per instrument per snapshot  ·  PK: business_date + trader_id + instrument_id + snapshot_type</t>
         </is>
@@ -37786,7 +37911,7 @@
       </c>
     </row>
     <row r="2" ht="14" customHeight="1">
-      <c r="A2" s="8" t="inlineStr">
+      <c r="A2" s="42" t="inlineStr">
         <is>
           <t>Fact  ·  Grain: one row per trader per business date  ·  PK: business_date + trader_id</t>
         </is>
@@ -38280,7 +38405,7 @@
       </c>
     </row>
     <row r="2" ht="14" customHeight="1">
-      <c r="A2" s="8" t="inlineStr">
+      <c r="A2" s="42" t="inlineStr">
         <is>
           <t>Fact  ·  Grain: one row per settlement leg  ·  PK: trade_id + settlement_leg</t>
         </is>

--- a/Trade-Surveillance-Data-Schema.xlsx
+++ b/Trade-Surveillance-Data-Schema.xlsx
@@ -801,7 +801,7 @@
 </file>
 
 <file path=xl/tables/table28.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="28" name="PanelLineage" displayName="PanelLineage" ref="A4:H36" headerRowCount="1">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="28" name="PanelLineage" displayName="PanelLineage" ref="A4:H38" headerRowCount="1">
   <autoFilter ref="A4:H36"/>
   <tableColumns count="8">
     <tableColumn id="1" name="Tab"/>
@@ -1328,7 +1328,7 @@
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>24 tables across 5 layers: core facts, supporting facts, dimensions, reference data, and one derived aggregate. 9 asset classes and 30 products are covered. All 58 detection rules and all 31 dashboard panels are traced back to the fields that feed them.</t>
+          <t>24 tables across 5 layers: core facts, supporting facts, dimensions, reference data, and one derived aggregate. 9 asset classes and 30 products are covered. All 58 detection rules and all 33 dashboard panels are traced back to the fields that feed them.</t>
         </is>
       </c>
     </row>
@@ -8731,7 +8731,7 @@
       </c>
       <c r="J5" s="10" t="inlineStr">
         <is>
-          <t>Trade Activity (all 10 panels), Trade Activity TimeSeries, Trade Blotter, and the evidence behind all 58 rules</t>
+          <t>Trade Activity (all 13 panels), Trade Activity TimeSeries, Trade Blotter, and the evidence behind all 58 rules</t>
         </is>
       </c>
     </row>
@@ -26817,7 +26817,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BN900"/>
+  <dimension ref="A1:BN65"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -33745,7 +33745,6 @@
       <c r="BM63" s="46" t="n"/>
       <c r="BN63" s="46" t="n"/>
     </row>
-    <row r="64"/>
     <row r="65">
       <c r="A65" s="47" t="inlineStr">
         <is>
@@ -33939,7 +33938,6 @@
         <v>1</v>
       </c>
     </row>
-    <row r="900"/>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -33952,7 +33950,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H36"/>
+  <dimension ref="A1:H38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -33975,7 +33973,7 @@
     <row r="2" ht="14" customHeight="1">
       <c r="A2" s="42" t="inlineStr">
         <is>
-          <t>All 31 panels across the 8 dashboard tabs. If a panel is not needed, the tables in its row may still be required by others — check '01 Table Index' before dropping anything. The eleven Trade Activity panels are drawn in a measure the reader chooses — deals and notional, or P&amp;L and margin — so each one has two readings of the same cut and needs the revenue fields as well as the volume ones.</t>
+          <t>All 33 panels across the 8 dashboard tabs. If a panel is not needed, the tables in its row may still be required by others — check '01 Table Index' before dropping anything. The thirteen Trade Activity panels are drawn in a measure the reader chooses — deals and notional, or P&amp;L and margin — so each one has two readings of the same cut and needs the revenue fields as well as the volume ones.</t>
         </is>
       </c>
     </row>
@@ -34022,1344 +34020,1428 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="18" t="inlineStr">
+      <c r="A5" s="21" t="inlineStr">
         <is>
           <t>Surveillance Overview</t>
         </is>
       </c>
-      <c r="B5" s="19" t="inlineStr">
+      <c r="B5" s="22" t="inlineStr">
         <is>
           <t>Detection volume — daily</t>
         </is>
       </c>
-      <c r="C5" s="10" t="inlineStr">
+      <c r="C5" s="13" t="inlineStr">
         <is>
           <t>Column, daily</t>
         </is>
       </c>
-      <c r="D5" s="10" t="inlineStr">
+      <c r="D5" s="13" t="inlineStr">
         <is>
           <t>Count of alerts</t>
         </is>
       </c>
-      <c r="E5" s="10" t="inlineStr">
+      <c r="E5" s="13" t="inlineStr">
         <is>
           <t>alert_date, severity</t>
         </is>
       </c>
-      <c r="F5" s="10" t="inlineStr">
+      <c r="F5" s="13" t="inlineStr">
         <is>
           <t>FACT_ALERT</t>
         </is>
       </c>
-      <c r="G5" s="10" t="inlineStr">
+      <c r="G5" s="13" t="inlineStr">
         <is>
           <t>alert_date, severity</t>
         </is>
       </c>
-      <c r="H5" s="10" t="inlineStr">
+      <c r="H5" s="13" t="inlineStr">
         <is>
           <t>Zero-alert days must render as zero, not as a gap — a missing bar and a quiet day look identical otherwise.</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="21" t="inlineStr">
+      <c r="A6" s="18" t="inlineStr">
         <is>
           <t>Surveillance Overview</t>
         </is>
       </c>
-      <c r="B6" s="22" t="inlineStr">
+      <c r="B6" s="19" t="inlineStr">
         <is>
           <t>Alert volume by month</t>
         </is>
       </c>
-      <c r="C6" s="13" t="inlineStr">
+      <c r="C6" s="10" t="inlineStr">
         <is>
           <t>Column, monthly</t>
         </is>
       </c>
-      <c r="D6" s="13" t="inlineStr">
+      <c r="D6" s="10" t="inlineStr">
         <is>
           <t>Count of alerts</t>
         </is>
       </c>
-      <c r="E6" s="13" t="inlineStr">
+      <c r="E6" s="10" t="inlineStr">
         <is>
           <t>alert_date month, severity</t>
         </is>
       </c>
-      <c r="F6" s="13" t="inlineStr">
+      <c r="F6" s="10" t="inlineStr">
         <is>
           <t>FACT_ALERT</t>
         </is>
       </c>
-      <c r="G6" s="13" t="inlineStr">
+      <c r="G6" s="10" t="inlineStr">
         <is>
           <t>alert_date, severity</t>
         </is>
       </c>
-      <c r="H6" s="13" t="inlineStr">
+      <c r="H6" s="10" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="18" t="inlineStr">
+      <c r="A7" s="21" t="inlineStr">
         <is>
           <t>Surveillance Overview</t>
         </is>
       </c>
-      <c r="B7" s="19" t="inlineStr">
+      <c r="B7" s="22" t="inlineStr">
         <is>
           <t>Severity mix</t>
         </is>
       </c>
-      <c r="C7" s="10" t="inlineStr">
+      <c r="C7" s="13" t="inlineStr">
         <is>
           <t>Stacked bar</t>
         </is>
       </c>
-      <c r="D7" s="10" t="inlineStr">
+      <c r="D7" s="13" t="inlineStr">
         <is>
           <t>Count of alerts</t>
         </is>
       </c>
-      <c r="E7" s="10" t="inlineStr">
+      <c r="E7" s="13" t="inlineStr">
         <is>
           <t>severity</t>
         </is>
       </c>
-      <c r="F7" s="10" t="inlineStr">
+      <c r="F7" s="13" t="inlineStr">
         <is>
           <t>FACT_ALERT</t>
         </is>
       </c>
-      <c r="G7" s="10" t="inlineStr">
+      <c r="G7" s="13" t="inlineStr">
         <is>
           <t>severity</t>
         </is>
       </c>
-      <c r="H7" s="10" t="inlineStr">
+      <c r="H7" s="13" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="21" t="inlineStr">
+      <c r="A8" s="18" t="inlineStr">
         <is>
           <t>Surveillance Overview</t>
         </is>
       </c>
-      <c r="B8" s="22" t="inlineStr">
+      <c r="B8" s="19" t="inlineStr">
         <is>
           <t>Disposition</t>
         </is>
       </c>
-      <c r="C8" s="13" t="inlineStr">
+      <c r="C8" s="10" t="inlineStr">
         <is>
           <t>Stacked bar</t>
         </is>
       </c>
-      <c r="D8" s="13" t="inlineStr">
+      <c r="D8" s="10" t="inlineStr">
         <is>
           <t>Count of alerts</t>
         </is>
       </c>
-      <c r="E8" s="13" t="inlineStr">
+      <c r="E8" s="10" t="inlineStr">
         <is>
           <t>status</t>
         </is>
       </c>
-      <c r="F8" s="13" t="inlineStr">
+      <c r="F8" s="10" t="inlineStr">
         <is>
           <t>FACT_ALERT</t>
         </is>
       </c>
-      <c r="G8" s="13" t="inlineStr">
+      <c r="G8" s="10" t="inlineStr">
         <is>
           <t>status</t>
         </is>
       </c>
-      <c r="H8" s="13" t="inlineStr">
+      <c r="H8" s="10" t="inlineStr">
         <is>
           <t>Terminal and in-flight statuses must be distinguishable.</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="18" t="inlineStr">
+      <c r="A9" s="21" t="inlineStr">
         <is>
           <t>Surveillance Overview</t>
         </is>
       </c>
-      <c r="B9" s="19" t="inlineStr">
+      <c r="B9" s="22" t="inlineStr">
         <is>
           <t>Typology fingerprint</t>
         </is>
       </c>
-      <c r="C9" s="10" t="inlineStr">
+      <c r="C9" s="13" t="inlineStr">
         <is>
           <t>Small-multiple grid</t>
         </is>
       </c>
-      <c r="D9" s="10" t="inlineStr">
+      <c r="D9" s="13" t="inlineStr">
         <is>
           <t>Count of alerts</t>
         </is>
       </c>
-      <c r="E9" s="10" t="inlineStr">
+      <c r="E9" s="13" t="inlineStr">
         <is>
           <t>rule_category x month</t>
         </is>
       </c>
-      <c r="F9" s="10" t="inlineStr">
+      <c r="F9" s="13" t="inlineStr">
         <is>
           <t>FACT_ALERT + REF_RULE</t>
         </is>
       </c>
-      <c r="G9" s="10" t="inlineStr">
+      <c r="G9" s="13" t="inlineStr">
         <is>
           <t>rule_category, alert_date</t>
         </is>
       </c>
-      <c r="H9" s="10" t="inlineStr">
+      <c r="H9" s="13" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="21" t="inlineStr">
+      <c r="A10" s="18" t="inlineStr">
         <is>
           <t>Surveillance Overview</t>
         </is>
       </c>
-      <c r="B10" s="22" t="inlineStr">
+      <c r="B10" s="19" t="inlineStr">
         <is>
           <t>Booking-hour profile</t>
         </is>
       </c>
-      <c r="C10" s="13" t="inlineStr">
+      <c r="C10" s="10" t="inlineStr">
         <is>
           <t>Heat strip</t>
         </is>
       </c>
-      <c r="D10" s="13" t="inlineStr">
+      <c r="D10" s="10" t="inlineStr">
         <is>
           <t>Count of alerts</t>
         </is>
       </c>
-      <c r="E10" s="13" t="inlineStr">
+      <c r="E10" s="10" t="inlineStr">
         <is>
           <t>alert_hour x day of week</t>
         </is>
       </c>
-      <c r="F10" s="13" t="inlineStr">
+      <c r="F10" s="10" t="inlineStr">
         <is>
           <t>FACT_ALERT</t>
         </is>
       </c>
-      <c r="G10" s="13" t="inlineStr">
+      <c r="G10" s="10" t="inlineStr">
         <is>
           <t>alert_hour, alert_date</t>
         </is>
       </c>
-      <c r="H10" s="13" t="inlineStr">
+      <c r="H10" s="10" t="inlineStr">
         <is>
           <t>Hour must be local to the desk, derived through DIM_DESK.timezone.</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="18" t="inlineStr">
+      <c r="A11" s="21" t="inlineStr">
         <is>
           <t>Surveillance Overview</t>
         </is>
       </c>
-      <c r="B11" s="19" t="inlineStr">
+      <c r="B11" s="22" t="inlineStr">
         <is>
           <t>Detection heatmap</t>
         </is>
       </c>
-      <c r="C11" s="10" t="inlineStr">
+      <c r="C11" s="13" t="inlineStr">
         <is>
           <t>Matrix</t>
         </is>
       </c>
-      <c r="D11" s="10" t="inlineStr">
+      <c r="D11" s="13" t="inlineStr">
         <is>
           <t>Count of alerts</t>
         </is>
       </c>
-      <c r="E11" s="10" t="inlineStr">
+      <c r="E11" s="13" t="inlineStr">
         <is>
           <t>rule_id x desk_id (or trader_id)</t>
         </is>
       </c>
-      <c r="F11" s="10" t="inlineStr">
+      <c r="F11" s="13" t="inlineStr">
         <is>
           <t>FACT_ALERT + REF_RULE + DIM_DESK</t>
         </is>
       </c>
-      <c r="G11" s="10" t="inlineStr">
+      <c r="G11" s="13" t="inlineStr">
         <is>
           <t>rule_id, desk_id, trader_id</t>
         </is>
       </c>
-      <c r="H11" s="10" t="inlineStr">
+      <c r="H11" s="13" t="inlineStr">
         <is>
           <t>Cell counts must reconcile exactly with the Detection queue when a cell is clicked. Same filter predicate, one source.</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="21" t="inlineStr">
+      <c r="A12" s="18" t="inlineStr">
         <is>
           <t>Surveillance Overview</t>
         </is>
       </c>
-      <c r="B12" s="22" t="inlineStr">
+      <c r="B12" s="19" t="inlineStr">
         <is>
           <t>Top rules by hits</t>
         </is>
       </c>
-      <c r="C12" s="13" t="inlineStr">
+      <c r="C12" s="10" t="inlineStr">
         <is>
           <t>Bar</t>
         </is>
       </c>
-      <c r="D12" s="13" t="inlineStr">
+      <c r="D12" s="10" t="inlineStr">
         <is>
           <t>Count of alerts</t>
         </is>
       </c>
-      <c r="E12" s="13" t="inlineStr">
+      <c r="E12" s="10" t="inlineStr">
         <is>
           <t>rule_id</t>
         </is>
       </c>
-      <c r="F12" s="13" t="inlineStr">
+      <c r="F12" s="10" t="inlineStr">
         <is>
           <t>FACT_ALERT + REF_RULE</t>
         </is>
       </c>
-      <c r="G12" s="13" t="inlineStr">
+      <c r="G12" s="10" t="inlineStr">
         <is>
           <t>rule_id, rule_name</t>
         </is>
       </c>
-      <c r="H12" s="13" t="inlineStr">
+      <c r="H12" s="10" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="18" t="inlineStr">
+      <c r="A13" s="21" t="inlineStr">
         <is>
           <t>Surveillance Overview</t>
         </is>
       </c>
-      <c r="B13" s="19" t="inlineStr">
+      <c r="B13" s="22" t="inlineStr">
         <is>
           <t>Open queue by age</t>
         </is>
       </c>
-      <c r="C13" s="10" t="inlineStr">
+      <c r="C13" s="13" t="inlineStr">
         <is>
           <t>Bar</t>
         </is>
       </c>
-      <c r="D13" s="10" t="inlineStr">
+      <c r="D13" s="13" t="inlineStr">
         <is>
           <t>Count of open alerts</t>
         </is>
       </c>
-      <c r="E13" s="10" t="inlineStr">
+      <c r="E13" s="13" t="inlineStr">
         <is>
           <t>Days since raised_timestamp</t>
         </is>
       </c>
-      <c r="F13" s="10" t="inlineStr">
+      <c r="F13" s="13" t="inlineStr">
         <is>
           <t>FACT_ALERT</t>
         </is>
       </c>
-      <c r="G13" s="10" t="inlineStr">
+      <c r="G13" s="13" t="inlineStr">
         <is>
           <t>raised_timestamp, status</t>
         </is>
       </c>
-      <c r="H13" s="10" t="inlineStr">
+      <c r="H13" s="13" t="inlineStr">
         <is>
           <t>Age is measured against now, so this panel changes without the data changing. Freeze the as-of time per render.</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="21" t="inlineStr">
+      <c r="A14" s="18" t="inlineStr">
         <is>
           <t>Surveillance Overview</t>
         </is>
       </c>
-      <c r="B14" s="22" t="inlineStr">
+      <c r="B14" s="19" t="inlineStr">
         <is>
           <t>Highest-risk traders</t>
         </is>
       </c>
-      <c r="C14" s="13" t="inlineStr">
+      <c r="C14" s="10" t="inlineStr">
         <is>
           <t>Ranked bar</t>
         </is>
       </c>
-      <c r="D14" s="13" t="inlineStr">
+      <c r="D14" s="10" t="inlineStr">
         <is>
           <t>risk_index</t>
         </is>
       </c>
-      <c r="E14" s="13" t="inlineStr">
+      <c r="E14" s="10" t="inlineStr">
         <is>
           <t>trader_id</t>
         </is>
       </c>
-      <c r="F14" s="13" t="inlineStr">
+      <c r="F14" s="10" t="inlineStr">
         <is>
           <t>DIM_TRADER + FACT_ALERT</t>
         </is>
       </c>
-      <c r="G14" s="13" t="inlineStr">
+      <c r="G14" s="10" t="inlineStr">
         <is>
           <t>risk_index, trader_name</t>
         </is>
       </c>
-      <c r="H14" s="13" t="inlineStr">
+      <c r="H14" s="10" t="inlineStr">
         <is>
           <t>Publish the risk_index weighting alongside the panel.</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="18" t="inlineStr">
+      <c r="A15" s="21" t="inlineStr">
         <is>
           <t>Trade Activity</t>
         </is>
       </c>
-      <c r="B15" s="19" t="inlineStr">
+      <c r="B15" s="22" t="inlineStr">
         <is>
           <t>Deal volume by month</t>
         </is>
       </c>
-      <c r="C15" s="10" t="inlineStr">
+      <c r="C15" s="13" t="inlineStr">
         <is>
           <t>Column</t>
         </is>
       </c>
-      <c r="D15" s="10" t="inlineStr">
+      <c r="D15" s="13" t="inlineStr">
         <is>
           <t>Count of deals and notional, or P&amp;L</t>
         </is>
       </c>
-      <c r="E15" s="10" t="inlineStr">
+      <c r="E15" s="13" t="inlineStr">
         <is>
           <t>trade_date month</t>
         </is>
       </c>
-      <c r="F15" s="10" t="inlineStr">
+      <c r="F15" s="13" t="inlineStr">
         <is>
           <t>FACT_TRADE</t>
         </is>
       </c>
-      <c r="G15" s="10" t="inlineStr">
+      <c r="G15" s="13" t="inlineStr">
         <is>
           <t>trade_date, notional_usd, total_revenue_usd</t>
         </is>
       </c>
-      <c r="H15" s="10" t="inlineStr">
+      <c r="H15" s="13" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="21" t="inlineStr">
+      <c r="A16" s="18" t="inlineStr">
         <is>
           <t>Trade Activity</t>
         </is>
       </c>
-      <c r="B16" s="22" t="inlineStr">
+      <c r="B16" s="19" t="inlineStr">
         <is>
           <t>Asset class mix</t>
         </is>
       </c>
-      <c r="C16" s="13" t="inlineStr">
+      <c r="C16" s="10" t="inlineStr">
         <is>
           <t>Stacked bar</t>
         </is>
       </c>
-      <c r="D16" s="13" t="inlineStr">
+      <c r="D16" s="10" t="inlineStr">
         <is>
           <t>Notional, or share of P&amp;L</t>
         </is>
       </c>
-      <c r="E16" s="13" t="inlineStr">
+      <c r="E16" s="10" t="inlineStr">
         <is>
           <t>asset_class</t>
         </is>
       </c>
-      <c r="F16" s="13" t="inlineStr">
+      <c r="F16" s="10" t="inlineStr">
         <is>
           <t>FACT_TRADE + DIM_PRODUCT</t>
         </is>
       </c>
-      <c r="G16" s="13" t="inlineStr">
+      <c r="G16" s="10" t="inlineStr">
         <is>
           <t>asset_class, notional_usd, total_revenue_usd</t>
         </is>
       </c>
-      <c r="H16" s="13" t="inlineStr">
+      <c r="H16" s="10" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="18" t="inlineStr">
+      <c r="A17" s="21" t="inlineStr">
         <is>
           <t>Trade Activity</t>
         </is>
       </c>
-      <c r="B17" s="19" t="inlineStr">
+      <c r="B17" s="22" t="inlineStr">
         <is>
           <t>Booking channel</t>
         </is>
       </c>
-      <c r="C17" s="10" t="inlineStr">
+      <c r="C17" s="13" t="inlineStr">
         <is>
           <t>Stacked bar</t>
         </is>
       </c>
-      <c r="D17" s="10" t="inlineStr">
+      <c r="D17" s="13" t="inlineStr">
         <is>
           <t>Count of deals, or share of P&amp;L</t>
         </is>
       </c>
-      <c r="E17" s="10" t="inlineStr">
+      <c r="E17" s="13" t="inlineStr">
         <is>
           <t>channel</t>
         </is>
       </c>
-      <c r="F17" s="10" t="inlineStr">
+      <c r="F17" s="13" t="inlineStr">
         <is>
           <t>FACT_TRADE</t>
         </is>
       </c>
-      <c r="G17" s="10" t="inlineStr">
+      <c r="G17" s="13" t="inlineStr">
         <is>
           <t>channel, total_revenue_usd</t>
         </is>
       </c>
-      <c r="H17" s="10" t="inlineStr">
+      <c r="H17" s="13" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="21" t="inlineStr">
+      <c r="A18" s="18" t="inlineStr">
         <is>
           <t>Trade Activity</t>
         </is>
       </c>
-      <c r="B18" s="22" t="inlineStr">
+      <c r="B18" s="19" t="inlineStr">
+        <is>
+          <t>Execution hours</t>
+        </is>
+      </c>
+      <c r="C18" s="10" t="inlineStr">
+        <is>
+          <t>Column, 24 bins</t>
+        </is>
+      </c>
+      <c r="D18" s="10" t="inlineStr">
+        <is>
+          <t>Count of deals, or P&amp;L</t>
+        </is>
+      </c>
+      <c r="E18" s="10" t="inlineStr">
+        <is>
+          <t>Hour of exec_timestamp</t>
+        </is>
+      </c>
+      <c r="F18" s="10" t="inlineStr">
+        <is>
+          <t>FACT_TRADE + DIM_DESK</t>
+        </is>
+      </c>
+      <c r="G18" s="10" t="inlineStr">
+        <is>
+          <t>exec_timestamp, timezone, total_revenue_usd</t>
+        </is>
+      </c>
+      <c r="H18" s="10" t="inlineStr">
+        <is>
+          <t>Bin in the desk's local time. A UTC-binned clock is wrong for two of the three regions.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="21" t="inlineStr">
+        <is>
+          <t>Trade Activity</t>
+        </is>
+      </c>
+      <c r="B19" s="22" t="inlineStr">
+        <is>
+          <t>Ticket size distribution</t>
+        </is>
+      </c>
+      <c r="C19" s="13" t="inlineStr">
+        <is>
+          <t>Column</t>
+        </is>
+      </c>
+      <c r="D19" s="13" t="inlineStr">
+        <is>
+          <t>Count of deals, or P&amp;L</t>
+        </is>
+      </c>
+      <c r="E19" s="13" t="inlineStr">
+        <is>
+          <t>size_band</t>
+        </is>
+      </c>
+      <c r="F19" s="13" t="inlineStr">
+        <is>
+          <t>FACT_TRADE</t>
+        </is>
+      </c>
+      <c r="G19" s="13" t="inlineStr">
+        <is>
+          <t>size_band, notional_usd, total_revenue_usd</t>
+        </is>
+      </c>
+      <c r="H19" s="13" t="inlineStr">
+        <is>
+          <t>Band boundaries come from the warehouse, not the UI.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="18" t="inlineStr">
+        <is>
+          <t>Trade Activity</t>
+        </is>
+      </c>
+      <c r="B20" s="19" t="inlineStr">
+        <is>
+          <t>Tenor profile</t>
+        </is>
+      </c>
+      <c r="C20" s="10" t="inlineStr">
+        <is>
+          <t>Column</t>
+        </is>
+      </c>
+      <c r="D20" s="10" t="inlineStr">
+        <is>
+          <t>Count of deals, or P&amp;L</t>
+        </is>
+      </c>
+      <c r="E20" s="10" t="inlineStr">
+        <is>
+          <t>tenor_band</t>
+        </is>
+      </c>
+      <c r="F20" s="10" t="inlineStr">
+        <is>
+          <t>FACT_TRADE</t>
+        </is>
+      </c>
+      <c r="G20" s="10" t="inlineStr">
+        <is>
+          <t>tenor_band, tenor_years, total_revenue_usd</t>
+        </is>
+      </c>
+      <c r="H20" s="10" t="inlineStr">
+        <is>
+          <t>Requires tenor_years as a number. A tenor label alone cannot be bucketed or sorted.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="21" t="inlineStr">
+        <is>
+          <t>Trade Activity</t>
+        </is>
+      </c>
+      <c r="B21" s="22" t="inlineStr">
+        <is>
+          <t>Desk</t>
+        </is>
+      </c>
+      <c r="C21" s="13" t="inlineStr">
+        <is>
+          <t>Ranked bar</t>
+        </is>
+      </c>
+      <c r="D21" s="13" t="inlineStr">
+        <is>
+          <t>Count of deals, or P&amp;L</t>
+        </is>
+      </c>
+      <c r="E21" s="13" t="inlineStr">
+        <is>
+          <t>desk_id</t>
+        </is>
+      </c>
+      <c r="F21" s="13" t="inlineStr">
+        <is>
+          <t>FACT_TRADE + DIM_DESK</t>
+        </is>
+      </c>
+      <c r="G21" s="13" t="inlineStr">
+        <is>
+          <t>desk_id, desk_name, asset_class, total_revenue_usd</t>
+        </is>
+      </c>
+      <c r="H21" s="13" t="inlineStr">
+        <is>
+          <t>Sum on FACT_TRADE.desk_id as booked, not on the trader's current desk — a trader who moved mid-year must leave each deal on the desk it was booked under. Bar colour is the desk's main asset class by deal count.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="18" t="inlineStr">
+        <is>
+          <t>Trade Activity</t>
+        </is>
+      </c>
+      <c r="B22" s="19" t="inlineStr">
         <is>
           <t>Transaction count by product</t>
         </is>
       </c>
-      <c r="C18" s="13" t="inlineStr">
+      <c r="C22" s="10" t="inlineStr">
         <is>
           <t>Bar</t>
         </is>
       </c>
-      <c r="D18" s="13" t="inlineStr">
+      <c r="D22" s="10" t="inlineStr">
         <is>
           <t>Count of deals, or P&amp;L</t>
         </is>
       </c>
-      <c r="E18" s="13" t="inlineStr">
+      <c r="E22" s="10" t="inlineStr">
         <is>
           <t>product</t>
         </is>
       </c>
-      <c r="F18" s="13" t="inlineStr">
+      <c r="F22" s="10" t="inlineStr">
         <is>
           <t>FACT_TRADE + DIM_PRODUCT</t>
         </is>
       </c>
-      <c r="G18" s="13" t="inlineStr">
+      <c r="G22" s="10" t="inlineStr">
         <is>
           <t>product, total_revenue_usd</t>
         </is>
       </c>
-      <c r="H18" s="13" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="18" t="inlineStr">
+      <c r="H22" s="10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="21" t="inlineStr">
         <is>
           <t>Trade Activity</t>
         </is>
       </c>
-      <c r="B19" s="19" t="inlineStr">
+      <c r="B23" s="22" t="inlineStr">
         <is>
           <t>Volume by product</t>
         </is>
       </c>
-      <c r="C19" s="10" t="inlineStr">
+      <c r="C23" s="13" t="inlineStr">
         <is>
           <t>Bar</t>
         </is>
       </c>
-      <c r="D19" s="10" t="inlineStr">
+      <c r="D23" s="13" t="inlineStr">
         <is>
           <t>Notional, or P&amp;L per $1m traded (margin)</t>
         </is>
       </c>
-      <c r="E19" s="10" t="inlineStr">
+      <c r="E23" s="13" t="inlineStr">
         <is>
           <t>product</t>
         </is>
       </c>
-      <c r="F19" s="10" t="inlineStr">
+      <c r="F23" s="13" t="inlineStr">
         <is>
           <t>FACT_TRADE + DIM_PRODUCT</t>
         </is>
       </c>
-      <c r="G19" s="10" t="inlineStr">
+      <c r="G23" s="13" t="inlineStr">
         <is>
           <t>product, notional_usd, total_revenue_usd</t>
         </is>
       </c>
-      <c r="H19" s="10" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="21" t="inlineStr">
+      <c r="H23" s="13" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="18" t="inlineStr">
         <is>
           <t>Trade Activity</t>
         </is>
       </c>
-      <c r="B20" s="22" t="inlineStr">
+      <c r="B24" s="19" t="inlineStr">
         <is>
           <t>Transaction count by counterparty</t>
         </is>
       </c>
-      <c r="C20" s="13" t="inlineStr">
+      <c r="C24" s="10" t="inlineStr">
         <is>
           <t>Bar</t>
         </is>
       </c>
-      <c r="D20" s="13" t="inlineStr">
+      <c r="D24" s="10" t="inlineStr">
         <is>
           <t>Count of deals, or P&amp;L</t>
         </is>
       </c>
-      <c r="E20" s="13" t="inlineStr">
+      <c r="E24" s="10" t="inlineStr">
         <is>
           <t>counterparty_id</t>
         </is>
       </c>
-      <c r="F20" s="13" t="inlineStr">
+      <c r="F24" s="10" t="inlineStr">
         <is>
           <t>FACT_TRADE + DIM_COUNTERPARTY</t>
         </is>
       </c>
-      <c r="G20" s="13" t="inlineStr">
+      <c r="G24" s="10" t="inlineStr">
         <is>
           <t>counterparty_id, counterparty_name, total_revenue_usd</t>
         </is>
       </c>
-      <c r="H20" s="13" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="18" t="inlineStr">
+      <c r="H24" s="10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="21" t="inlineStr">
         <is>
           <t>Trade Activity</t>
         </is>
       </c>
-      <c r="B21" s="19" t="inlineStr">
+      <c r="B25" s="22" t="inlineStr">
         <is>
           <t>Volume by counterparties</t>
         </is>
       </c>
-      <c r="C21" s="10" t="inlineStr">
+      <c r="C25" s="13" t="inlineStr">
         <is>
           <t>Bar</t>
         </is>
       </c>
-      <c r="D21" s="10" t="inlineStr">
+      <c r="D25" s="13" t="inlineStr">
         <is>
           <t>Notional, or P&amp;L per $1m traded (margin)</t>
         </is>
       </c>
-      <c r="E21" s="10" t="inlineStr">
+      <c r="E25" s="13" t="inlineStr">
         <is>
           <t>counterparty_id</t>
         </is>
       </c>
-      <c r="F21" s="10" t="inlineStr">
+      <c r="F25" s="13" t="inlineStr">
         <is>
           <t>FACT_TRADE + DIM_COUNTERPARTY</t>
         </is>
       </c>
-      <c r="G21" s="10" t="inlineStr">
+      <c r="G25" s="13" t="inlineStr">
         <is>
           <t>counterparty_id, notional_usd, total_revenue_usd</t>
         </is>
       </c>
-      <c r="H21" s="10" t="inlineStr">
+      <c r="H25" s="13" t="inlineStr">
         <is>
           <t>Roll up to parent_lei as well — entity-level concentration understates group exposure.</t>
         </is>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" s="21" t="inlineStr">
+    <row r="26">
+      <c r="A26" s="18" t="inlineStr">
         <is>
           <t>Trade Activity</t>
         </is>
       </c>
-      <c r="B22" s="22" t="inlineStr">
-        <is>
-          <t>Execution hours</t>
-        </is>
-      </c>
-      <c r="C22" s="13" t="inlineStr">
-        <is>
-          <t>Column, 24 bins</t>
-        </is>
-      </c>
-      <c r="D22" s="13" t="inlineStr">
+      <c r="B26" s="19" t="inlineStr">
+        <is>
+          <t>Trader map</t>
+        </is>
+      </c>
+      <c r="C26" s="10" t="inlineStr">
+        <is>
+          <t>Treemap, traders grouped by desk</t>
+        </is>
+      </c>
+      <c r="D26" s="10" t="inlineStr">
         <is>
           <t>Count of deals, or P&amp;L</t>
         </is>
       </c>
-      <c r="E22" s="13" t="inlineStr">
-        <is>
-          <t>Hour of exec_timestamp</t>
-        </is>
-      </c>
-      <c r="F22" s="13" t="inlineStr">
-        <is>
-          <t>FACT_TRADE + DIM_DESK</t>
-        </is>
-      </c>
-      <c r="G22" s="13" t="inlineStr">
-        <is>
-          <t>exec_timestamp, timezone, total_revenue_usd</t>
-        </is>
-      </c>
-      <c r="H22" s="13" t="inlineStr">
-        <is>
-          <t>Bin in the desk's local time. A UTC-binned clock is wrong for two of the three regions.</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="18" t="inlineStr">
+      <c r="E26" s="10" t="inlineStr">
+        <is>
+          <t>trader_id within desk_id</t>
+        </is>
+      </c>
+      <c r="F26" s="10" t="inlineStr">
+        <is>
+          <t>FACT_TRADE + DIM_TRADER + DIM_DESK</t>
+        </is>
+      </c>
+      <c r="G26" s="10" t="inlineStr">
+        <is>
+          <t>trader_id, trader_name, desk_id, asset_class, total_revenue_usd</t>
+        </is>
+      </c>
+      <c r="H26" s="10" t="inlineStr">
+        <is>
+          <t>Tile area is proportional to the measure and cannot be negative: a trader with a loss in the scope, or too small to draw, is listed under the chart rather than dropped. Colour is the trader's main asset class by deal count.</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="21" t="inlineStr">
         <is>
           <t>Trade Activity</t>
         </is>
       </c>
-      <c r="B23" s="19" t="inlineStr">
-        <is>
-          <t>Ticket size distribution</t>
-        </is>
-      </c>
-      <c r="C23" s="10" t="inlineStr">
+      <c r="B27" s="22" t="inlineStr">
+        <is>
+          <t>Trading activity by trader</t>
+        </is>
+      </c>
+      <c r="C27" s="13" t="inlineStr">
+        <is>
+          <t>Ranked bar, selectable</t>
+        </is>
+      </c>
+      <c r="D27" s="13" t="inlineStr">
+        <is>
+          <t>Count of deals, notional, tenor spread, or P&amp;L</t>
+        </is>
+      </c>
+      <c r="E27" s="13" t="inlineStr">
+        <is>
+          <t>trader_id</t>
+        </is>
+      </c>
+      <c r="F27" s="13" t="inlineStr">
+        <is>
+          <t>FACT_TRADE + DIM_TRADER</t>
+        </is>
+      </c>
+      <c r="G27" s="13" t="inlineStr">
+        <is>
+          <t>trader_id, trader_name, notional_usd, total_revenue_usd</t>
+        </is>
+      </c>
+      <c r="H27" s="13" t="inlineStr">
+        <is>
+          <t>Selecting a bar re-scopes every panel above it, so it must share the trader key exactly.</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="18" t="inlineStr">
+        <is>
+          <t>Trade Activity TimeSeries</t>
+        </is>
+      </c>
+      <c r="B28" s="19" t="inlineStr">
+        <is>
+          <t>Trade activity time series</t>
+        </is>
+      </c>
+      <c r="C28" s="10" t="inlineStr">
+        <is>
+          <t>Scatter, one mark per deal</t>
+        </is>
+      </c>
+      <c r="D28" s="10" t="inlineStr">
+        <is>
+          <t>Notional (mark size)</t>
+        </is>
+      </c>
+      <c r="E28" s="10" t="inlineStr">
+        <is>
+          <t>exec_timestamp x notional, encoded by asset_class / trader_id / desk_id</t>
+        </is>
+      </c>
+      <c r="F28" s="10" t="inlineStr">
+        <is>
+          <t>FACT_TRADE + DIM_PRODUCT + DIM_TRADER + DIM_DESK + REF_CALENDAR</t>
+        </is>
+      </c>
+      <c r="G28" s="10" t="inlineStr">
+        <is>
+          <t>trade_id, exec_timestamp, notional_usd, asset_class, trader_id, desk_id, is_weekend</t>
+        </is>
+      </c>
+      <c r="H28" s="10" t="inlineStr">
+        <is>
+          <t>The only panel that reads deal-level rows at full resolution. exec_timestamp precision to the second sets the maximum zoom.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="21" t="inlineStr">
+        <is>
+          <t>Detections</t>
+        </is>
+      </c>
+      <c r="B29" s="22" t="inlineStr">
+        <is>
+          <t>Detection queue</t>
+        </is>
+      </c>
+      <c r="C29" s="13" t="inlineStr">
+        <is>
+          <t>Table with drill-down</t>
+        </is>
+      </c>
+      <c r="D29" s="13" t="inlineStr">
+        <is>
+          <t>Count and notional</t>
+        </is>
+      </c>
+      <c r="E29" s="13" t="inlineStr">
+        <is>
+          <t>alert_id</t>
+        </is>
+      </c>
+      <c r="F29" s="13" t="inlineStr">
+        <is>
+          <t>FACT_ALERT + FACT_ALERT_TRADE + FACT_ALERT_EVIDENCE + FACT_ALERT_AUDIT</t>
+        </is>
+      </c>
+      <c r="G29" s="13" t="inlineStr">
+        <is>
+          <t>alert_id, score, severity, status, cited trade_ids</t>
+        </is>
+      </c>
+      <c r="H29" s="13" t="inlineStr">
+        <is>
+          <t>Clicking an alert opens the cited deals and the evidence lines. All four tables are needed for the drawer.</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="18" t="inlineStr">
+        <is>
+          <t>Rule Library</t>
+        </is>
+      </c>
+      <c r="B30" s="19" t="inlineStr">
+        <is>
+          <t>Rule library</t>
+        </is>
+      </c>
+      <c r="C30" s="10" t="inlineStr">
+        <is>
+          <t>Card list</t>
+        </is>
+      </c>
+      <c r="D30" s="10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E30" s="10" t="inlineStr">
+        <is>
+          <t>rule_id</t>
+        </is>
+      </c>
+      <c r="F30" s="10" t="inlineStr">
+        <is>
+          <t>REF_RULE + REF_DATA_ELEMENT</t>
+        </is>
+      </c>
+      <c r="G30" s="10" t="inlineStr">
+        <is>
+          <t>rule_id, logic, baseline_used, required elements</t>
+        </is>
+      </c>
+      <c r="H30" s="10" t="inlineStr">
+        <is>
+          <t>The data-requirements section of each card is generated from the rule-to-element mapping, not written by hand.</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="21" t="inlineStr">
+        <is>
+          <t>Trade Blotter</t>
+        </is>
+      </c>
+      <c r="B31" s="22" t="inlineStr">
+        <is>
+          <t>Trade blotter</t>
+        </is>
+      </c>
+      <c r="C31" s="13" t="inlineStr">
+        <is>
+          <t>Table</t>
+        </is>
+      </c>
+      <c r="D31" s="13" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E31" s="13" t="inlineStr">
+        <is>
+          <t>trade_id</t>
+        </is>
+      </c>
+      <c r="F31" s="13" t="inlineStr">
+        <is>
+          <t>FACT_TRADE + FACT_TRADE_AMEND + FACT_ALERT_TRADE</t>
+        </is>
+      </c>
+      <c r="G31" s="13" t="inlineStr">
+        <is>
+          <t>All FACT_TRADE display columns</t>
+        </is>
+      </c>
+      <c r="H31" s="13" t="inlineStr">
+        <is>
+          <t>The lowest-level view. Every column here has to be present on FACT_TRADE or joinable from it in one hop.</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="18" t="inlineStr">
+        <is>
+          <t>Traders &amp; Groups</t>
+        </is>
+      </c>
+      <c r="B32" s="19" t="inlineStr">
+        <is>
+          <t>Alerts against volume</t>
+        </is>
+      </c>
+      <c r="C32" s="10" t="inlineStr">
+        <is>
+          <t>Scatter</t>
+        </is>
+      </c>
+      <c r="D32" s="10" t="inlineStr">
+        <is>
+          <t>Alert count against notional</t>
+        </is>
+      </c>
+      <c r="E32" s="10" t="inlineStr">
+        <is>
+          <t>trader_id</t>
+        </is>
+      </c>
+      <c r="F32" s="10" t="inlineStr">
+        <is>
+          <t>FACT_ALERT + FACT_TRADE + DIM_TRADER</t>
+        </is>
+      </c>
+      <c r="G32" s="10" t="inlineStr">
+        <is>
+          <t>trader_id, alert count, notional_usd</t>
+        </is>
+      </c>
+      <c r="H32" s="10" t="inlineStr">
+        <is>
+          <t>Both measures must be filtered by the same period, or the ratio is nonsense.</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="21" t="inlineStr">
+        <is>
+          <t>Traders &amp; Groups</t>
+        </is>
+      </c>
+      <c r="B33" s="22" t="inlineStr">
+        <is>
+          <t>Detection heatmap</t>
+        </is>
+      </c>
+      <c r="C33" s="13" t="inlineStr">
+        <is>
+          <t>Matrix</t>
+        </is>
+      </c>
+      <c r="D33" s="13" t="inlineStr">
+        <is>
+          <t>Count of alerts</t>
+        </is>
+      </c>
+      <c r="E33" s="13" t="inlineStr">
+        <is>
+          <t>trader_id x rule_id</t>
+        </is>
+      </c>
+      <c r="F33" s="13" t="inlineStr">
+        <is>
+          <t>FACT_ALERT + REF_RULE + DIM_TRADER</t>
+        </is>
+      </c>
+      <c r="G33" s="13" t="inlineStr">
+        <is>
+          <t>trader_id, rule_id</t>
+        </is>
+      </c>
+      <c r="H33" s="13" t="inlineStr">
+        <is>
+          <t>Same panel and same source as the Overview heatmap, transposed.</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="18" t="inlineStr">
+        <is>
+          <t>Traders &amp; Groups</t>
+        </is>
+      </c>
+      <c r="B34" s="19" t="inlineStr">
+        <is>
+          <t>Desks</t>
+        </is>
+      </c>
+      <c r="C34" s="10" t="inlineStr">
+        <is>
+          <t>Summary table</t>
+        </is>
+      </c>
+      <c r="D34" s="10" t="inlineStr">
+        <is>
+          <t>Counts, notional, alert rate</t>
+        </is>
+      </c>
+      <c r="E34" s="10" t="inlineStr">
+        <is>
+          <t>desk_id</t>
+        </is>
+      </c>
+      <c r="F34" s="10" t="inlineStr">
+        <is>
+          <t>DIM_DESK + FACT_TRADE + FACT_ALERT</t>
+        </is>
+      </c>
+      <c r="G34" s="10" t="inlineStr">
+        <is>
+          <t>desk_id, desk_name, region</t>
+        </is>
+      </c>
+      <c r="H34" s="10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="21" t="inlineStr">
+        <is>
+          <t>Traders &amp; Groups</t>
+        </is>
+      </c>
+      <c r="B35" s="22" t="inlineStr">
+        <is>
+          <t>Trader risk index</t>
+        </is>
+      </c>
+      <c r="C35" s="13" t="inlineStr">
+        <is>
+          <t>Ranked bar</t>
+        </is>
+      </c>
+      <c r="D35" s="13" t="inlineStr">
+        <is>
+          <t>risk_index</t>
+        </is>
+      </c>
+      <c r="E35" s="13" t="inlineStr">
+        <is>
+          <t>trader_id</t>
+        </is>
+      </c>
+      <c r="F35" s="13" t="inlineStr">
+        <is>
+          <t>DIM_TRADER + FACT_ALERT + AGG_TRADER_BASELINE</t>
+        </is>
+      </c>
+      <c r="G35" s="13" t="inlineStr">
+        <is>
+          <t>risk_index and its component inputs</t>
+        </is>
+      </c>
+      <c r="H35" s="13" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="18" t="inlineStr">
+        <is>
+          <t>Review Log</t>
+        </is>
+      </c>
+      <c r="B36" s="19" t="inlineStr">
+        <is>
+          <t>Decisions by month</t>
+        </is>
+      </c>
+      <c r="C36" s="10" t="inlineStr">
         <is>
           <t>Column</t>
         </is>
       </c>
-      <c r="D23" s="10" t="inlineStr">
-        <is>
-          <t>Count of deals, or P&amp;L</t>
-        </is>
-      </c>
-      <c r="E23" s="10" t="inlineStr">
-        <is>
-          <t>size_band</t>
-        </is>
-      </c>
-      <c r="F23" s="10" t="inlineStr">
-        <is>
-          <t>FACT_TRADE</t>
-        </is>
-      </c>
-      <c r="G23" s="10" t="inlineStr">
-        <is>
-          <t>size_band, notional_usd, total_revenue_usd</t>
-        </is>
-      </c>
-      <c r="H23" s="10" t="inlineStr">
-        <is>
-          <t>Band boundaries come from the warehouse, not the UI.</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="21" t="inlineStr">
-        <is>
-          <t>Trade Activity</t>
-        </is>
-      </c>
-      <c r="B24" s="22" t="inlineStr">
-        <is>
-          <t>Tenor profile</t>
-        </is>
-      </c>
-      <c r="C24" s="13" t="inlineStr">
-        <is>
-          <t>Column</t>
-        </is>
-      </c>
-      <c r="D24" s="13" t="inlineStr">
-        <is>
-          <t>Count of deals, or P&amp;L</t>
-        </is>
-      </c>
-      <c r="E24" s="13" t="inlineStr">
-        <is>
-          <t>tenor_band</t>
-        </is>
-      </c>
-      <c r="F24" s="13" t="inlineStr">
-        <is>
-          <t>FACT_TRADE</t>
-        </is>
-      </c>
-      <c r="G24" s="13" t="inlineStr">
-        <is>
-          <t>tenor_band, tenor_years, total_revenue_usd</t>
-        </is>
-      </c>
-      <c r="H24" s="13" t="inlineStr">
-        <is>
-          <t>Requires tenor_years as a number. A tenor label alone cannot be bucketed or sorted.</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="18" t="inlineStr">
-        <is>
-          <t>Trade Activity</t>
-        </is>
-      </c>
-      <c r="B25" s="19" t="inlineStr">
-        <is>
-          <t>Trading activity by trader</t>
-        </is>
-      </c>
-      <c r="C25" s="10" t="inlineStr">
-        <is>
-          <t>Ranked bar, selectable</t>
-        </is>
-      </c>
-      <c r="D25" s="10" t="inlineStr">
-        <is>
-          <t>Count of deals, notional, tenor spread, or P&amp;L</t>
-        </is>
-      </c>
-      <c r="E25" s="10" t="inlineStr">
-        <is>
-          <t>trader_id</t>
-        </is>
-      </c>
-      <c r="F25" s="10" t="inlineStr">
-        <is>
-          <t>FACT_TRADE + DIM_TRADER</t>
-        </is>
-      </c>
-      <c r="G25" s="10" t="inlineStr">
-        <is>
-          <t>trader_id, trader_name, notional_usd, total_revenue_usd</t>
-        </is>
-      </c>
-      <c r="H25" s="10" t="inlineStr">
-        <is>
-          <t>Selecting a bar re-scopes every panel above it, so it must share the trader key exactly.</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="21" t="inlineStr">
-        <is>
-          <t>Trade Activity TimeSeries</t>
-        </is>
-      </c>
-      <c r="B26" s="22" t="inlineStr">
-        <is>
-          <t>Trade activity time series</t>
-        </is>
-      </c>
-      <c r="C26" s="13" t="inlineStr">
-        <is>
-          <t>Scatter, one mark per deal</t>
-        </is>
-      </c>
-      <c r="D26" s="13" t="inlineStr">
-        <is>
-          <t>Notional (mark size)</t>
-        </is>
-      </c>
-      <c r="E26" s="13" t="inlineStr">
-        <is>
-          <t>exec_timestamp x notional, encoded by asset_class / trader_id / desk_id</t>
-        </is>
-      </c>
-      <c r="F26" s="13" t="inlineStr">
-        <is>
-          <t>FACT_TRADE + DIM_PRODUCT + DIM_TRADER + DIM_DESK + REF_CALENDAR</t>
-        </is>
-      </c>
-      <c r="G26" s="13" t="inlineStr">
-        <is>
-          <t>trade_id, exec_timestamp, notional_usd, asset_class, trader_id, desk_id, is_weekend</t>
-        </is>
-      </c>
-      <c r="H26" s="13" t="inlineStr">
-        <is>
-          <t>The only panel that reads deal-level rows at full resolution. exec_timestamp precision to the second sets the maximum zoom.</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="18" t="inlineStr">
-        <is>
-          <t>Detections</t>
-        </is>
-      </c>
-      <c r="B27" s="19" t="inlineStr">
-        <is>
-          <t>Detection queue</t>
-        </is>
-      </c>
-      <c r="C27" s="10" t="inlineStr">
-        <is>
-          <t>Table with drill-down</t>
-        </is>
-      </c>
-      <c r="D27" s="10" t="inlineStr">
-        <is>
-          <t>Count and notional</t>
-        </is>
-      </c>
-      <c r="E27" s="10" t="inlineStr">
+      <c r="D36" s="10" t="inlineStr">
+        <is>
+          <t>Count of decisions</t>
+        </is>
+      </c>
+      <c r="E36" s="10" t="inlineStr">
+        <is>
+          <t>reviewed_timestamp month, status</t>
+        </is>
+      </c>
+      <c r="F36" s="10" t="inlineStr">
+        <is>
+          <t>FACT_ALERT</t>
+        </is>
+      </c>
+      <c r="G36" s="10" t="inlineStr">
+        <is>
+          <t>reviewed_timestamp, status</t>
+        </is>
+      </c>
+      <c r="H36" s="10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="21" t="inlineStr">
+        <is>
+          <t>Review Log</t>
+        </is>
+      </c>
+      <c r="B37" s="22" t="inlineStr">
+        <is>
+          <t>Reason codes used</t>
+        </is>
+      </c>
+      <c r="C37" s="13" t="inlineStr">
+        <is>
+          <t>Bar</t>
+        </is>
+      </c>
+      <c r="D37" s="13" t="inlineStr">
+        <is>
+          <t>Count of decisions</t>
+        </is>
+      </c>
+      <c r="E37" s="13" t="inlineStr">
+        <is>
+          <t>disposition_reason</t>
+        </is>
+      </c>
+      <c r="F37" s="13" t="inlineStr">
+        <is>
+          <t>FACT_ALERT</t>
+        </is>
+      </c>
+      <c r="G37" s="13" t="inlineStr">
+        <is>
+          <t>disposition_reason</t>
+        </is>
+      </c>
+      <c r="H37" s="13" t="inlineStr">
+        <is>
+          <t>Requires a controlled reason-code list. Free text here makes the panel unusable.</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="18" t="inlineStr">
+        <is>
+          <t>Review Log</t>
+        </is>
+      </c>
+      <c r="B38" s="19" t="inlineStr">
+        <is>
+          <t>Disposition log</t>
+        </is>
+      </c>
+      <c r="C38" s="10" t="inlineStr">
+        <is>
+          <t>Table</t>
+        </is>
+      </c>
+      <c r="D38" s="10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E38" s="10" t="inlineStr">
         <is>
           <t>alert_id</t>
         </is>
       </c>
-      <c r="F27" s="10" t="inlineStr">
-        <is>
-          <t>FACT_ALERT + FACT_ALERT_TRADE + FACT_ALERT_EVIDENCE + FACT_ALERT_AUDIT</t>
-        </is>
-      </c>
-      <c r="G27" s="10" t="inlineStr">
-        <is>
-          <t>alert_id, score, severity, status, cited trade_ids</t>
-        </is>
-      </c>
-      <c r="H27" s="10" t="inlineStr">
-        <is>
-          <t>Clicking an alert opens the cited deals and the evidence lines. All four tables are needed for the drawer.</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="21" t="inlineStr">
-        <is>
-          <t>Rule Library</t>
-        </is>
-      </c>
-      <c r="B28" s="22" t="inlineStr">
-        <is>
-          <t>Rule library</t>
-        </is>
-      </c>
-      <c r="C28" s="13" t="inlineStr">
-        <is>
-          <t>Card list</t>
-        </is>
-      </c>
-      <c r="D28" s="13" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E28" s="13" t="inlineStr">
-        <is>
-          <t>rule_id</t>
-        </is>
-      </c>
-      <c r="F28" s="13" t="inlineStr">
-        <is>
-          <t>REF_RULE + REF_DATA_ELEMENT</t>
-        </is>
-      </c>
-      <c r="G28" s="13" t="inlineStr">
-        <is>
-          <t>rule_id, logic, baseline_used, required elements</t>
-        </is>
-      </c>
-      <c r="H28" s="13" t="inlineStr">
-        <is>
-          <t>The data-requirements section of each card is generated from the rule-to-element mapping, not written by hand.</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="18" t="inlineStr">
-        <is>
-          <t>Trade Blotter</t>
-        </is>
-      </c>
-      <c r="B29" s="19" t="inlineStr">
-        <is>
-          <t>Trade blotter</t>
-        </is>
-      </c>
-      <c r="C29" s="10" t="inlineStr">
-        <is>
-          <t>Table</t>
-        </is>
-      </c>
-      <c r="D29" s="10" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E29" s="10" t="inlineStr">
-        <is>
-          <t>trade_id</t>
-        </is>
-      </c>
-      <c r="F29" s="10" t="inlineStr">
-        <is>
-          <t>FACT_TRADE + FACT_TRADE_AMEND + FACT_ALERT_TRADE</t>
-        </is>
-      </c>
-      <c r="G29" s="10" t="inlineStr">
-        <is>
-          <t>All FACT_TRADE display columns</t>
-        </is>
-      </c>
-      <c r="H29" s="10" t="inlineStr">
-        <is>
-          <t>The lowest-level view. Every column here has to be present on FACT_TRADE or joinable from it in one hop.</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="21" t="inlineStr">
-        <is>
-          <t>Traders &amp; Groups</t>
-        </is>
-      </c>
-      <c r="B30" s="22" t="inlineStr">
-        <is>
-          <t>Alerts against volume</t>
-        </is>
-      </c>
-      <c r="C30" s="13" t="inlineStr">
-        <is>
-          <t>Scatter</t>
-        </is>
-      </c>
-      <c r="D30" s="13" t="inlineStr">
-        <is>
-          <t>Alert count against notional</t>
-        </is>
-      </c>
-      <c r="E30" s="13" t="inlineStr">
-        <is>
-          <t>trader_id</t>
-        </is>
-      </c>
-      <c r="F30" s="13" t="inlineStr">
-        <is>
-          <t>FACT_ALERT + FACT_TRADE + DIM_TRADER</t>
-        </is>
-      </c>
-      <c r="G30" s="13" t="inlineStr">
-        <is>
-          <t>trader_id, alert count, notional_usd</t>
-        </is>
-      </c>
-      <c r="H30" s="13" t="inlineStr">
-        <is>
-          <t>Both measures must be filtered by the same period, or the ratio is nonsense.</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="18" t="inlineStr">
-        <is>
-          <t>Traders &amp; Groups</t>
-        </is>
-      </c>
-      <c r="B31" s="19" t="inlineStr">
-        <is>
-          <t>Detection heatmap</t>
-        </is>
-      </c>
-      <c r="C31" s="10" t="inlineStr">
-        <is>
-          <t>Matrix</t>
-        </is>
-      </c>
-      <c r="D31" s="10" t="inlineStr">
-        <is>
-          <t>Count of alerts</t>
-        </is>
-      </c>
-      <c r="E31" s="10" t="inlineStr">
-        <is>
-          <t>trader_id x rule_id</t>
-        </is>
-      </c>
-      <c r="F31" s="10" t="inlineStr">
-        <is>
-          <t>FACT_ALERT + REF_RULE + DIM_TRADER</t>
-        </is>
-      </c>
-      <c r="G31" s="10" t="inlineStr">
-        <is>
-          <t>trader_id, rule_id</t>
-        </is>
-      </c>
-      <c r="H31" s="10" t="inlineStr">
-        <is>
-          <t>Same panel and same source as the Overview heatmap, transposed.</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="21" t="inlineStr">
-        <is>
-          <t>Traders &amp; Groups</t>
-        </is>
-      </c>
-      <c r="B32" s="22" t="inlineStr">
-        <is>
-          <t>Desks</t>
-        </is>
-      </c>
-      <c r="C32" s="13" t="inlineStr">
-        <is>
-          <t>Summary table</t>
-        </is>
-      </c>
-      <c r="D32" s="13" t="inlineStr">
-        <is>
-          <t>Counts, notional, alert rate</t>
-        </is>
-      </c>
-      <c r="E32" s="13" t="inlineStr">
-        <is>
-          <t>desk_id</t>
-        </is>
-      </c>
-      <c r="F32" s="13" t="inlineStr">
-        <is>
-          <t>DIM_DESK + FACT_TRADE + FACT_ALERT</t>
-        </is>
-      </c>
-      <c r="G32" s="13" t="inlineStr">
-        <is>
-          <t>desk_id, desk_name, region</t>
-        </is>
-      </c>
-      <c r="H32" s="13" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="18" t="inlineStr">
-        <is>
-          <t>Traders &amp; Groups</t>
-        </is>
-      </c>
-      <c r="B33" s="19" t="inlineStr">
-        <is>
-          <t>Trader risk index</t>
-        </is>
-      </c>
-      <c r="C33" s="10" t="inlineStr">
-        <is>
-          <t>Ranked bar</t>
-        </is>
-      </c>
-      <c r="D33" s="10" t="inlineStr">
-        <is>
-          <t>risk_index</t>
-        </is>
-      </c>
-      <c r="E33" s="10" t="inlineStr">
-        <is>
-          <t>trader_id</t>
-        </is>
-      </c>
-      <c r="F33" s="10" t="inlineStr">
-        <is>
-          <t>DIM_TRADER + FACT_ALERT + AGG_TRADER_BASELINE</t>
-        </is>
-      </c>
-      <c r="G33" s="10" t="inlineStr">
-        <is>
-          <t>risk_index and its component inputs</t>
-        </is>
-      </c>
-      <c r="H33" s="10" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="21" t="inlineStr">
-        <is>
-          <t>Review Log</t>
-        </is>
-      </c>
-      <c r="B34" s="22" t="inlineStr">
-        <is>
-          <t>Decisions by month</t>
-        </is>
-      </c>
-      <c r="C34" s="13" t="inlineStr">
-        <is>
-          <t>Column</t>
-        </is>
-      </c>
-      <c r="D34" s="13" t="inlineStr">
-        <is>
-          <t>Count of decisions</t>
-        </is>
-      </c>
-      <c r="E34" s="13" t="inlineStr">
-        <is>
-          <t>reviewed_timestamp month, status</t>
-        </is>
-      </c>
-      <c r="F34" s="13" t="inlineStr">
-        <is>
-          <t>FACT_ALERT</t>
-        </is>
-      </c>
-      <c r="G34" s="13" t="inlineStr">
-        <is>
-          <t>reviewed_timestamp, status</t>
-        </is>
-      </c>
-      <c r="H34" s="13" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="18" t="inlineStr">
-        <is>
-          <t>Review Log</t>
-        </is>
-      </c>
-      <c r="B35" s="19" t="inlineStr">
-        <is>
-          <t>Reason codes used</t>
-        </is>
-      </c>
-      <c r="C35" s="10" t="inlineStr">
-        <is>
-          <t>Bar</t>
-        </is>
-      </c>
-      <c r="D35" s="10" t="inlineStr">
-        <is>
-          <t>Count of decisions</t>
-        </is>
-      </c>
-      <c r="E35" s="10" t="inlineStr">
-        <is>
-          <t>disposition_reason</t>
-        </is>
-      </c>
-      <c r="F35" s="10" t="inlineStr">
-        <is>
-          <t>FACT_ALERT</t>
-        </is>
-      </c>
-      <c r="G35" s="10" t="inlineStr">
-        <is>
-          <t>disposition_reason</t>
-        </is>
-      </c>
-      <c r="H35" s="10" t="inlineStr">
-        <is>
-          <t>Requires a controlled reason-code list. Free text here makes the panel unusable.</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="21" t="inlineStr">
-        <is>
-          <t>Review Log</t>
-        </is>
-      </c>
-      <c r="B36" s="22" t="inlineStr">
-        <is>
-          <t>Disposition log</t>
-        </is>
-      </c>
-      <c r="C36" s="13" t="inlineStr">
-        <is>
-          <t>Table</t>
-        </is>
-      </c>
-      <c r="D36" s="13" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E36" s="13" t="inlineStr">
-        <is>
-          <t>alert_id</t>
-        </is>
-      </c>
-      <c r="F36" s="13" t="inlineStr">
+      <c r="F38" s="10" t="inlineStr">
         <is>
           <t>FACT_ALERT + FACT_ALERT_AUDIT</t>
         </is>
       </c>
-      <c r="G36" s="13" t="inlineStr">
+      <c r="G38" s="10" t="inlineStr">
         <is>
           <t>reviewer_id, reviewed_timestamp, status, disposition_reason, reviewer_note</t>
         </is>
       </c>
-      <c r="H36" s="13" t="inlineStr">
+      <c r="H38" s="10" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -36590,7 +36672,7 @@
       </c>
       <c r="C17" s="13" t="inlineStr">
         <is>
-          <t>TS-51 – TS-58, the eight revenue rules, and the P&amp;L view of all eleven Trade Activity panels.</t>
+          <t>TS-51 – TS-58, the eight revenue rules, and the P&amp;L view of all thirteen Trade Activity panels.</t>
         </is>
       </c>
       <c r="D17" s="13" t="inlineStr">

--- a/Trade-Surveillance-Data-Schema.xlsx
+++ b/Trade-Surveillance-Data-Schema.xlsx
@@ -1296,6 +1296,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
@@ -1308,6 +1309,7 @@
         </is>
       </c>
     </row>
+    <row r="5"/>
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
         <is>
@@ -1320,6 +1322,7 @@
         </is>
       </c>
     </row>
+    <row r="7"/>
     <row r="8">
       <c r="A8" s="3" t="inlineStr">
         <is>
@@ -1332,6 +1335,7 @@
         </is>
       </c>
     </row>
+    <row r="9"/>
     <row r="10">
       <c r="A10" s="3" t="inlineStr">
         <is>
@@ -1351,6 +1355,7 @@
         </is>
       </c>
     </row>
+    <row r="11"/>
     <row r="12">
       <c r="A12" s="3" t="inlineStr">
         <is>
@@ -1372,6 +1377,7 @@
         </is>
       </c>
     </row>
+    <row r="13"/>
     <row r="14">
       <c r="A14" s="3" t="inlineStr">
         <is>
@@ -1387,6 +1393,7 @@
         </is>
       </c>
     </row>
+    <row r="15"/>
     <row r="16">
       <c r="A16" s="5" t="inlineStr">
         <is>
@@ -1402,6 +1409,7 @@
         </is>
       </c>
     </row>
+    <row r="17"/>
     <row r="18">
       <c r="A18" s="3" t="inlineStr">
         <is>
@@ -1414,6 +1422,7 @@
         </is>
       </c>
     </row>
+    <row r="19"/>
     <row r="20">
       <c r="A20" s="3" t="inlineStr">
         <is>
@@ -1426,6 +1435,7 @@
         </is>
       </c>
     </row>
+    <row r="21"/>
     <row r="22">
       <c r="A22" s="3" t="inlineStr">
         <is>
@@ -1438,6 +1448,7 @@
         </is>
       </c>
     </row>
+    <row r="23"/>
     <row r="24">
       <c r="A24" s="3" t="inlineStr">
         <is>
@@ -1499,6 +1510,7 @@
         </is>
       </c>
     </row>
+    <row r="4"/>
     <row r="5" ht="30" customHeight="1">
       <c r="A5" s="9" t="inlineStr">
         <is>
@@ -1938,6 +1950,7 @@
         </is>
       </c>
     </row>
+    <row r="4"/>
     <row r="5" ht="30" customHeight="1">
       <c r="A5" s="9" t="inlineStr">
         <is>
@@ -3081,7 +3094,7 @@
       </c>
       <c r="I25" s="13" t="inlineStr">
         <is>
-          <t>M. Sundaram</t>
+          <t>M. Sakamoto</t>
         </is>
       </c>
       <c r="J25" s="13" t="inlineStr">
@@ -3587,6 +3600,7 @@
         </is>
       </c>
     </row>
+    <row r="4"/>
     <row r="5" ht="30" customHeight="1">
       <c r="A5" s="9" t="inlineStr">
         <is>
@@ -3916,6 +3930,7 @@
         </is>
       </c>
     </row>
+    <row r="4"/>
     <row r="5" ht="30" customHeight="1">
       <c r="A5" s="9" t="inlineStr">
         <is>
@@ -4355,6 +4370,7 @@
         </is>
       </c>
     </row>
+    <row r="4"/>
     <row r="5" ht="30" customHeight="1">
       <c r="A5" s="9" t="inlineStr">
         <is>
@@ -4618,7 +4634,7 @@
       </c>
       <c r="I9" s="13" t="inlineStr">
         <is>
-          <t>M. Sundaram</t>
+          <t>M. Sakamoto</t>
         </is>
       </c>
       <c r="J9" s="13" t="inlineStr">
@@ -4849,6 +4865,7 @@
         </is>
       </c>
     </row>
+    <row r="4"/>
     <row r="5" ht="30" customHeight="1">
       <c r="A5" s="9" t="inlineStr">
         <is>
@@ -5112,7 +5129,7 @@
       </c>
       <c r="I9" s="13" t="inlineStr">
         <is>
-          <t>Malcolm Ferris</t>
+          <t>Masato Fujii</t>
         </is>
       </c>
       <c r="J9" s="13" t="inlineStr">
@@ -5387,7 +5404,7 @@
       </c>
       <c r="I14" s="10" t="inlineStr">
         <is>
-          <t>Nadia Farrell</t>
+          <t>Naomi Fujiwara</t>
         </is>
       </c>
       <c r="J14" s="10" t="inlineStr">
@@ -5948,6 +5965,7 @@
         </is>
       </c>
     </row>
+    <row r="4"/>
     <row r="5" ht="30" customHeight="1">
       <c r="A5" s="9" t="inlineStr">
         <is>
@@ -6662,6 +6680,7 @@
         </is>
       </c>
     </row>
+    <row r="4"/>
     <row r="5" ht="30" customHeight="1">
       <c r="A5" s="9" t="inlineStr">
         <is>
@@ -7486,6 +7505,7 @@
         </is>
       </c>
     </row>
+    <row r="4"/>
     <row r="5" ht="30" customHeight="1">
       <c r="A5" s="9" t="inlineStr">
         <is>
@@ -8035,6 +8055,7 @@
         </is>
       </c>
     </row>
+    <row r="4"/>
     <row r="5" ht="30" customHeight="1">
       <c r="A5" s="9" t="inlineStr">
         <is>
@@ -8631,6 +8652,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4" ht="30" customHeight="1">
       <c r="A4" s="9" t="inlineStr">
         <is>
@@ -9983,6 +10005,7 @@
         </is>
       </c>
     </row>
+    <row r="4"/>
     <row r="5" ht="30" customHeight="1">
       <c r="A5" s="9" t="inlineStr">
         <is>
@@ -10532,6 +10555,7 @@
         </is>
       </c>
     </row>
+    <row r="4"/>
     <row r="5" ht="30" customHeight="1">
       <c r="A5" s="9" t="inlineStr">
         <is>
@@ -11136,6 +11160,7 @@
         </is>
       </c>
     </row>
+    <row r="4"/>
     <row r="5" ht="30" customHeight="1">
       <c r="A5" s="9" t="inlineStr">
         <is>
@@ -11630,6 +11655,7 @@
         </is>
       </c>
     </row>
+    <row r="4"/>
     <row r="5" ht="30" customHeight="1">
       <c r="A5" s="9" t="inlineStr">
         <is>
@@ -12014,6 +12040,7 @@
         </is>
       </c>
     </row>
+    <row r="4"/>
     <row r="5" ht="30" customHeight="1">
       <c r="A5" s="9" t="inlineStr">
         <is>
@@ -13828,6 +13855,7 @@
         </is>
       </c>
     </row>
+    <row r="4"/>
     <row r="5" ht="30" customHeight="1">
       <c r="A5" s="9" t="inlineStr">
         <is>
@@ -14542,6 +14570,7 @@
         </is>
       </c>
     </row>
+    <row r="4"/>
     <row r="5" ht="30" customHeight="1">
       <c r="A5" s="9" t="inlineStr">
         <is>
@@ -15023,6 +15052,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4" ht="30" customHeight="1">
       <c r="A4" s="9" t="inlineStr">
         <is>
@@ -17810,6 +17840,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4" ht="30" customHeight="1">
       <c r="A4" s="9" t="inlineStr">
         <is>
@@ -19064,6 +19095,7 @@
         </is>
       </c>
     </row>
+    <row r="26"/>
     <row r="27">
       <c r="A27" s="30" t="inlineStr">
         <is>
@@ -19167,6 +19199,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4" ht="30" customHeight="1">
       <c r="A4" s="9" t="inlineStr">
         <is>
@@ -21426,6 +21459,7 @@
         </is>
       </c>
     </row>
+    <row r="4"/>
     <row r="5" ht="30" customHeight="1">
       <c r="A5" s="9" t="inlineStr">
         <is>
@@ -24440,6 +24474,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4" ht="30" customHeight="1">
       <c r="A4" s="9" t="inlineStr">
         <is>
@@ -26902,6 +26937,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="42" t="inlineStr">
         <is>
@@ -33745,6 +33781,7 @@
       <c r="BM63" s="46" t="n"/>
       <c r="BN63" s="46" t="n"/>
     </row>
+    <row r="64"/>
     <row r="65">
       <c r="A65" s="47" t="inlineStr">
         <is>
@@ -33977,6 +34014,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4" ht="30" customHeight="1">
       <c r="A4" s="9" t="inlineStr">
         <is>
@@ -35486,6 +35524,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4" ht="30" customHeight="1">
       <c r="A4" s="9" t="inlineStr">
         <is>
@@ -36308,6 +36347,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4" ht="30" customHeight="1">
       <c r="A4" s="9" t="inlineStr">
         <is>
@@ -36738,6 +36778,7 @@
         </is>
       </c>
     </row>
+    <row r="4"/>
     <row r="5" ht="30" customHeight="1">
       <c r="A5" s="9" t="inlineStr">
         <is>
@@ -37342,6 +37383,7 @@
         </is>
       </c>
     </row>
+    <row r="4"/>
     <row r="5" ht="30" customHeight="1">
       <c r="A5" s="9" t="inlineStr">
         <is>
@@ -38166,6 +38208,7 @@
         </is>
       </c>
     </row>
+    <row r="4"/>
     <row r="5" ht="30" customHeight="1">
       <c r="A5" s="9" t="inlineStr">
         <is>
@@ -38770,6 +38813,7 @@
         </is>
       </c>
     </row>
+    <row r="4"/>
     <row r="5" ht="30" customHeight="1">
       <c r="A5" s="9" t="inlineStr">
         <is>
@@ -39429,6 +39473,7 @@
         </is>
       </c>
     </row>
+    <row r="4"/>
     <row r="5" ht="30" customHeight="1">
       <c r="A5" s="9" t="inlineStr">
         <is>
@@ -39923,6 +39968,7 @@
         </is>
       </c>
     </row>
+    <row r="4"/>
     <row r="5" ht="30" customHeight="1">
       <c r="A5" s="9" t="inlineStr">
         <is>

--- a/Trade-Surveillance-Data-Schema.xlsx
+++ b/Trade-Surveillance-Data-Schema.xlsx
@@ -1296,7 +1296,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
@@ -1309,7 +1308,6 @@
         </is>
       </c>
     </row>
-    <row r="5"/>
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
         <is>
@@ -1318,11 +1316,10 @@
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>Every field, enumeration, length and sample value in this workbook was extracted from the working dashboard, not drafted from a template. Field lengths under 'Data type / length' state the maximum observed in the prototype dataset (58,889 deals, 3,560 alerts, 68 traders, 12 desks, 198 instruments, 40 counterparties, 58 rules) and are marked as such. Size the production columns from your own data, using the observed value as a floor, not a ceiling.</t>
-        </is>
-      </c>
-    </row>
-    <row r="7"/>
+          <t>Every field, enumeration, length and sample value in this workbook was extracted from the working dashboard, not drafted from a template. Field lengths under 'Data type / length' state the maximum observed in the prototype dataset (60,198 deals, 3,724 alerts, 68 traders, 12 desks, 198 instruments, 40 counterparties, 58 rules) and are marked as such. Size the production columns from your own data, using the observed value as a floor, not a ceiling.</t>
+        </is>
+      </c>
+    </row>
     <row r="8">
       <c r="A8" s="3" t="inlineStr">
         <is>
@@ -1335,7 +1332,6 @@
         </is>
       </c>
     </row>
-    <row r="9"/>
     <row r="10">
       <c r="A10" s="3" t="inlineStr">
         <is>
@@ -1355,7 +1351,6 @@
         </is>
       </c>
     </row>
-    <row r="11"/>
     <row r="12">
       <c r="A12" s="3" t="inlineStr">
         <is>
@@ -1377,7 +1372,6 @@
         </is>
       </c>
     </row>
-    <row r="13"/>
     <row r="14">
       <c r="A14" s="3" t="inlineStr">
         <is>
@@ -1393,7 +1387,6 @@
         </is>
       </c>
     </row>
-    <row r="15"/>
     <row r="16">
       <c r="A16" s="5" t="inlineStr">
         <is>
@@ -1405,11 +1398,10 @@
         <is>
           <t>1. exec_timestamp must be a real execution time, to the second, with a timezone offset. 18 of the 58 rules and three panels are computed from it, and there is no safe default.
 2. market_mid must be a point-in-time snap at execution, not an end-of-day mark. Substituting the end-of-day mark changes what every Pricing rule tests, and the findings will not survive challenge.
-3. AGG_TRADER_BASELINE is not optional. 24 of the 50 rules read the trader's own trailing baseline directly and cannot run at all without it, and 41 of the 50 measure against a reference specific to the trader, instrument or product rather than a bank-wide fixed number.</t>
-        </is>
-      </c>
-    </row>
-    <row r="17"/>
+3. AGG_TRADER_BASELINE is not optional. 28 of the 58 rules read the trader's own trailing baseline directly and cannot run at all without it, and 49 of the 58 measure against a reference specific to the trader, instrument or product rather than a bank-wide fixed number.</t>
+        </is>
+      </c>
+    </row>
     <row r="18">
       <c r="A18" s="3" t="inlineStr">
         <is>
@@ -1422,7 +1414,6 @@
         </is>
       </c>
     </row>
-    <row r="19"/>
     <row r="20">
       <c r="A20" s="3" t="inlineStr">
         <is>
@@ -1435,7 +1426,6 @@
         </is>
       </c>
     </row>
-    <row r="21"/>
     <row r="22">
       <c r="A22" s="3" t="inlineStr">
         <is>
@@ -1448,7 +1438,6 @@
         </is>
       </c>
     </row>
-    <row r="23"/>
     <row r="24">
       <c r="A24" s="3" t="inlineStr">
         <is>
@@ -1510,7 +1499,6 @@
         </is>
       </c>
     </row>
-    <row r="4"/>
     <row r="5" ht="30" customHeight="1">
       <c r="A5" s="9" t="inlineStr">
         <is>
@@ -1946,11 +1934,10 @@
     <row r="3">
       <c r="A3" s="17" t="inlineStr">
         <is>
-          <t>Source: Surveillance engine, enriched by case management   |   Refresh: Written by the engine on each run; status updated by reviewers in real time   |   Volume: ~3.6k per rolling year in the prototype at current calibration   |   Priority: 1 — Blocking</t>
-        </is>
-      </c>
-    </row>
-    <row r="4"/>
+          <t>Source: Surveillance engine, enriched by case management   |   Refresh: Written by the engine on each run; status updated by reviewers in real time   |   Volume: ~3.7k per rolling year in the prototype at current calibration   |   Priority: 1 — Blocking</t>
+        </is>
+      </c>
+    </row>
     <row r="5" ht="30" customHeight="1">
       <c r="A5" s="9" t="inlineStr">
         <is>
@@ -2704,7 +2691,7 @@
       </c>
       <c r="H18" s="10" t="inlineStr">
         <is>
-          <t>0.97 .. 4,578 observed</t>
+          <t>0.97 .. 5,414 observed</t>
         </is>
       </c>
       <c r="I18" s="10" t="inlineStr">
@@ -2924,7 +2911,7 @@
       </c>
       <c r="H22" s="10" t="inlineStr">
         <is>
-          <t>19 codes observed — see Enumerations</t>
+          <t>18 codes — see Enumerations</t>
         </is>
       </c>
       <c r="I22" s="10" t="inlineStr">
@@ -3596,11 +3583,10 @@
     <row r="3">
       <c r="A3" s="17" t="inlineStr">
         <is>
-          <t>Source: Surveillance engine   |   Refresh: With the alert   |   Volume: 1 to 31 deals cited per alert, mean 2.8   |   Priority: 1 — Blocking</t>
-        </is>
-      </c>
-    </row>
-    <row r="4"/>
+          <t>Source: Surveillance engine   |   Refresh: With the alert   |   Volume: 1 to 35 deals cited per alert, mean 3.1   |   Priority: 1 — Blocking</t>
+        </is>
+      </c>
+    </row>
     <row r="5" ht="30" customHeight="1">
       <c r="A5" s="9" t="inlineStr">
         <is>
@@ -3819,7 +3805,7 @@
       </c>
       <c r="K8" s="10" t="inlineStr">
         <is>
-          <t>A pattern rule cites up to 31 deals; the reviewer needs to know which one actually breached and which are context. Without this the Detection queue drill-down cannot rank the blotter.</t>
+          <t>A pattern rule cites up to 35 deals; the reviewer needs to know which one actually breached and which are context. Without this the Detection queue drill-down cannot rank the blotter.</t>
         </is>
       </c>
     </row>
@@ -3930,7 +3916,6 @@
         </is>
       </c>
     </row>
-    <row r="4"/>
     <row r="5" ht="30" customHeight="1">
       <c r="A5" s="9" t="inlineStr">
         <is>
@@ -4119,7 +4104,7 @@
       </c>
       <c r="E8" s="10" t="inlineStr">
         <is>
-          <t>Free text. Observed 61 chars.</t>
+          <t>Free text. Observed 74 chars.</t>
         </is>
       </c>
       <c r="F8" s="12" t="inlineStr">
@@ -4169,12 +4154,12 @@
       </c>
       <c r="D9" s="13" t="inlineStr">
         <is>
-          <t>VARCHAR(200)</t>
+          <t>VARCHAR(500)</t>
         </is>
       </c>
       <c r="E9" s="13" t="inlineStr">
         <is>
-          <t>Free text. Observed 141 chars.</t>
+          <t>Free text. Observed 308 chars — TS-58 lists every client charged.</t>
         </is>
       </c>
       <c r="F9" s="12" t="inlineStr">
@@ -4370,7 +4355,6 @@
         </is>
       </c>
     </row>
-    <row r="4"/>
     <row r="5" ht="30" customHeight="1">
       <c r="A5" s="9" t="inlineStr">
         <is>
@@ -4865,7 +4849,6 @@
         </is>
       </c>
     </row>
-    <row r="4"/>
     <row r="5" ht="30" customHeight="1">
       <c r="A5" s="9" t="inlineStr">
         <is>
@@ -5109,7 +5092,7 @@
       </c>
       <c r="E9" s="13" t="inlineStr">
         <is>
-          <t>Free text. Observed 18 chars.</t>
+          <t>Free text. Observed 17 chars.</t>
         </is>
       </c>
       <c r="F9" s="12" t="inlineStr">
@@ -5384,7 +5367,7 @@
       </c>
       <c r="E14" s="10" t="inlineStr">
         <is>
-          <t>Free text. Observed 17 chars.</t>
+          <t>Free text. Observed 15 chars.</t>
         </is>
       </c>
       <c r="F14" s="12" t="inlineStr">
@@ -5965,7 +5948,6 @@
         </is>
       </c>
     </row>
-    <row r="4"/>
     <row r="5" ht="30" customHeight="1">
       <c r="A5" s="9" t="inlineStr">
         <is>
@@ -6680,7 +6662,6 @@
         </is>
       </c>
     </row>
-    <row r="4"/>
     <row r="5" ht="30" customHeight="1">
       <c r="A5" s="9" t="inlineStr">
         <is>
@@ -7505,7 +7486,6 @@
         </is>
       </c>
     </row>
-    <row r="4"/>
     <row r="5" ht="30" customHeight="1">
       <c r="A5" s="9" t="inlineStr">
         <is>
@@ -8055,7 +8035,6 @@
         </is>
       </c>
     </row>
-    <row r="4"/>
     <row r="5" ht="30" customHeight="1">
       <c r="A5" s="9" t="inlineStr">
         <is>
@@ -8652,7 +8631,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4" ht="30" customHeight="1">
       <c r="A4" s="9" t="inlineStr">
         <is>
@@ -8743,7 +8721,7 @@
       </c>
       <c r="H5" s="10" t="inlineStr">
         <is>
-          <t>~59k rows per rolling year in the prototype; size for your real daily deal count x 400 days</t>
+          <t>~60k rows per rolling year in the prototype; size for your real daily deal count x 400 days</t>
         </is>
       </c>
       <c r="I5" s="12" t="inlineStr">
@@ -8795,7 +8773,7 @@
       </c>
       <c r="H6" s="13" t="inlineStr">
         <is>
-          <t>7.1% of deals carry at least one amendment; 0.7% are cancelled</t>
+          <t>7.0% of deals carry at least one amendment; 0.7% are cancelled</t>
         </is>
       </c>
       <c r="I6" s="12" t="inlineStr">
@@ -9159,7 +9137,7 @@
       </c>
       <c r="H13" s="10" t="inlineStr">
         <is>
-          <t>~3.6k per rolling year in the prototype at current calibration</t>
+          <t>~3.7k per rolling year in the prototype at current calibration</t>
         </is>
       </c>
       <c r="I13" s="12" t="inlineStr">
@@ -9211,7 +9189,7 @@
       </c>
       <c r="H14" s="13" t="inlineStr">
         <is>
-          <t>1 to 31 deals cited per alert, mean 2.8</t>
+          <t>1 to 35 deals cited per alert, mean 3.1</t>
         </is>
       </c>
       <c r="I14" s="12" t="inlineStr">
@@ -10005,7 +9983,6 @@
         </is>
       </c>
     </row>
-    <row r="4"/>
     <row r="5" ht="30" customHeight="1">
       <c r="A5" s="9" t="inlineStr">
         <is>
@@ -10555,7 +10532,6 @@
         </is>
       </c>
     </row>
-    <row r="4"/>
     <row r="5" ht="30" customHeight="1">
       <c r="A5" s="9" t="inlineStr">
         <is>
@@ -11160,7 +11136,6 @@
         </is>
       </c>
     </row>
-    <row r="4"/>
     <row r="5" ht="30" customHeight="1">
       <c r="A5" s="9" t="inlineStr">
         <is>
@@ -11655,7 +11630,6 @@
         </is>
       </c>
     </row>
-    <row r="4"/>
     <row r="5" ht="30" customHeight="1">
       <c r="A5" s="9" t="inlineStr">
         <is>
@@ -12040,7 +12014,6 @@
         </is>
       </c>
     </row>
-    <row r="4"/>
     <row r="5" ht="30" customHeight="1">
       <c r="A5" s="9" t="inlineStr">
         <is>
@@ -13855,7 +13828,6 @@
         </is>
       </c>
     </row>
-    <row r="4"/>
     <row r="5" ht="30" customHeight="1">
       <c r="A5" s="9" t="inlineStr">
         <is>
@@ -14570,7 +14542,6 @@
         </is>
       </c>
     </row>
-    <row r="4"/>
     <row r="5" ht="30" customHeight="1">
       <c r="A5" s="9" t="inlineStr">
         <is>
@@ -15028,7 +14999,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E194"/>
+  <dimension ref="A1:E193"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -15052,7 +15023,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4" ht="30" customHeight="1">
       <c r="A4" s="9" t="inlineStr">
         <is>
@@ -17255,7 +17225,7 @@
       </c>
       <c r="E155" s="25" t="inlineStr">
         <is>
-          <t>19 codes. A controlled list is required — free text makes the Reason codes panel unusable.</t>
+          <t>18 codes. A controlled list is required — free text makes the Reason codes panel unusable.</t>
         </is>
       </c>
     </row>
@@ -17481,323 +17451,316 @@
       <c r="E172" s="13" t="inlineStr"/>
     </row>
     <row r="173">
-      <c r="A173" s="18" t="inlineStr"/>
-      <c r="B173" s="10" t="inlineStr"/>
-      <c r="C173" s="18" t="n">
-        <v>19</v>
-      </c>
-      <c r="D173" s="18" t="inlineStr"/>
-      <c r="E173" s="10" t="inlineStr"/>
+      <c r="A173" s="24" t="inlineStr">
+        <is>
+          <t>RULE_CATEGORY</t>
+        </is>
+      </c>
+      <c r="B173" s="25" t="inlineStr">
+        <is>
+          <t>REF_RULE.category, FACT_ALERT.rule_category</t>
+        </is>
+      </c>
+      <c r="C173" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="D173" s="26" t="inlineStr">
+        <is>
+          <t>Pricing</t>
+        </is>
+      </c>
+      <c r="E173" s="25" t="inlineStr">
+        <is>
+          <t>9 categories. These are the rows of the Detection heatmap.</t>
+        </is>
+      </c>
     </row>
     <row r="174">
-      <c r="A174" s="24" t="inlineStr">
-        <is>
-          <t>RULE_CATEGORY</t>
-        </is>
-      </c>
-      <c r="B174" s="25" t="inlineStr">
-        <is>
-          <t>REF_RULE.category, FACT_ALERT.rule_category</t>
-        </is>
-      </c>
-      <c r="C174" s="26" t="n">
+      <c r="A174" s="18" t="inlineStr"/>
+      <c r="B174" s="10" t="inlineStr"/>
+      <c r="C174" s="18" t="n">
+        <v>2</v>
+      </c>
+      <c r="D174" s="18" t="inlineStr">
+        <is>
+          <t>Booking integrity</t>
+        </is>
+      </c>
+      <c r="E174" s="10" t="inlineStr"/>
+    </row>
+    <row r="175">
+      <c r="A175" s="21" t="inlineStr"/>
+      <c r="B175" s="13" t="inlineStr"/>
+      <c r="C175" s="21" t="n">
+        <v>3</v>
+      </c>
+      <c r="D175" s="21" t="inlineStr">
+        <is>
+          <t>Market conduct</t>
+        </is>
+      </c>
+      <c r="E175" s="13" t="inlineStr"/>
+    </row>
+    <row r="176">
+      <c r="A176" s="18" t="inlineStr"/>
+      <c r="B176" s="10" t="inlineStr"/>
+      <c r="C176" s="18" t="n">
+        <v>4</v>
+      </c>
+      <c r="D176" s="18" t="inlineStr">
+        <is>
+          <t>Limits &amp; controls</t>
+        </is>
+      </c>
+      <c r="E176" s="10" t="inlineStr"/>
+    </row>
+    <row r="177">
+      <c r="A177" s="21" t="inlineStr"/>
+      <c r="B177" s="13" t="inlineStr"/>
+      <c r="C177" s="21" t="n">
+        <v>5</v>
+      </c>
+      <c r="D177" s="21" t="inlineStr">
+        <is>
+          <t>Valuation</t>
+        </is>
+      </c>
+      <c r="E177" s="13" t="inlineStr"/>
+    </row>
+    <row r="178">
+      <c r="A178" s="18" t="inlineStr"/>
+      <c r="B178" s="10" t="inlineStr"/>
+      <c r="C178" s="18" t="n">
+        <v>6</v>
+      </c>
+      <c r="D178" s="18" t="inlineStr">
+        <is>
+          <t>Client conduct</t>
+        </is>
+      </c>
+      <c r="E178" s="10" t="inlineStr"/>
+    </row>
+    <row r="179">
+      <c r="A179" s="21" t="inlineStr"/>
+      <c r="B179" s="13" t="inlineStr"/>
+      <c r="C179" s="21" t="n">
+        <v>7</v>
+      </c>
+      <c r="D179" s="21" t="inlineStr">
+        <is>
+          <t>Settlement</t>
+        </is>
+      </c>
+      <c r="E179" s="13" t="inlineStr"/>
+    </row>
+    <row r="180">
+      <c r="A180" s="18" t="inlineStr"/>
+      <c r="B180" s="10" t="inlineStr"/>
+      <c r="C180" s="18" t="n">
+        <v>8</v>
+      </c>
+      <c r="D180" s="18" t="inlineStr">
+        <is>
+          <t>Financing</t>
+        </is>
+      </c>
+      <c r="E180" s="10" t="inlineStr"/>
+    </row>
+    <row r="181">
+      <c r="A181" s="21" t="inlineStr"/>
+      <c r="B181" s="13" t="inlineStr"/>
+      <c r="C181" s="21" t="n">
+        <v>9</v>
+      </c>
+      <c r="D181" s="21" t="inlineStr">
+        <is>
+          <t>Information misuse</t>
+        </is>
+      </c>
+      <c r="E181" s="13" t="inlineStr"/>
+    </row>
+    <row r="182">
+      <c r="A182" s="24" t="inlineStr">
+        <is>
+          <t>AUDIT_ACTION</t>
+        </is>
+      </c>
+      <c r="B182" s="25" t="inlineStr">
+        <is>
+          <t>FACT_ALERT_AUDIT.action</t>
+        </is>
+      </c>
+      <c r="C182" s="26" t="n">
         <v>1</v>
       </c>
-      <c r="D174" s="26" t="inlineStr">
-        <is>
-          <t>Pricing</t>
-        </is>
-      </c>
-      <c r="E174" s="25" t="inlineStr">
-        <is>
-          <t>9 categories. These are the rows of the Detection heatmap.</t>
-        </is>
-      </c>
-    </row>
-    <row r="175">
-      <c r="A175" s="18" t="inlineStr"/>
-      <c r="B175" s="10" t="inlineStr"/>
-      <c r="C175" s="18" t="n">
+      <c r="D182" s="26" t="inlineStr">
+        <is>
+          <t>Alert raised</t>
+        </is>
+      </c>
+      <c r="E182" s="25" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" s="21" t="inlineStr"/>
+      <c r="B183" s="13" t="inlineStr"/>
+      <c r="C183" s="21" t="n">
         <v>2</v>
       </c>
-      <c r="D175" s="18" t="inlineStr">
-        <is>
-          <t>Booking integrity</t>
-        </is>
-      </c>
-      <c r="E175" s="10" t="inlineStr"/>
-    </row>
-    <row r="176">
-      <c r="A176" s="21" t="inlineStr"/>
-      <c r="B176" s="13" t="inlineStr"/>
-      <c r="C176" s="21" t="n">
+      <c r="D183" s="21" t="inlineStr">
+        <is>
+          <t>Assigned</t>
+        </is>
+      </c>
+      <c r="E183" s="13" t="inlineStr"/>
+    </row>
+    <row r="184">
+      <c r="A184" s="18" t="inlineStr"/>
+      <c r="B184" s="10" t="inlineStr"/>
+      <c r="C184" s="18" t="n">
         <v>3</v>
       </c>
-      <c r="D176" s="21" t="inlineStr">
-        <is>
-          <t>Market conduct</t>
-        </is>
-      </c>
-      <c r="E176" s="13" t="inlineStr"/>
-    </row>
-    <row r="177">
-      <c r="A177" s="18" t="inlineStr"/>
-      <c r="B177" s="10" t="inlineStr"/>
-      <c r="C177" s="18" t="n">
+      <c r="D184" s="18" t="inlineStr">
+        <is>
+          <t>Escalated to Investigations</t>
+        </is>
+      </c>
+      <c r="E184" s="10" t="inlineStr"/>
+    </row>
+    <row r="185">
+      <c r="A185" s="21" t="inlineStr"/>
+      <c r="B185" s="13" t="inlineStr"/>
+      <c r="C185" s="21" t="n">
         <v>4</v>
       </c>
-      <c r="D177" s="18" t="inlineStr">
-        <is>
-          <t>Limits &amp; controls</t>
-        </is>
-      </c>
-      <c r="E177" s="10" t="inlineStr"/>
-    </row>
-    <row r="178">
-      <c r="A178" s="21" t="inlineStr"/>
-      <c r="B178" s="13" t="inlineStr"/>
-      <c r="C178" s="21" t="n">
+      <c r="D185" s="21" t="inlineStr">
+        <is>
+          <t>Case opened</t>
+        </is>
+      </c>
+      <c r="E185" s="13" t="inlineStr"/>
+    </row>
+    <row r="186">
+      <c r="A186" s="18" t="inlineStr"/>
+      <c r="B186" s="10" t="inlineStr"/>
+      <c r="C186" s="18" t="n">
         <v>5</v>
       </c>
-      <c r="D178" s="21" t="inlineStr">
-        <is>
-          <t>Valuation</t>
-        </is>
-      </c>
-      <c r="E178" s="13" t="inlineStr"/>
-    </row>
-    <row r="179">
-      <c r="A179" s="18" t="inlineStr"/>
-      <c r="B179" s="10" t="inlineStr"/>
-      <c r="C179" s="18" t="n">
+      <c r="D186" s="18" t="inlineStr">
+        <is>
+          <t>Tagged suspicious</t>
+        </is>
+      </c>
+      <c r="E186" s="10" t="inlineStr"/>
+    </row>
+    <row r="187">
+      <c r="A187" s="21" t="inlineStr"/>
+      <c r="B187" s="13" t="inlineStr"/>
+      <c r="C187" s="21" t="n">
         <v>6</v>
       </c>
-      <c r="D179" s="18" t="inlineStr">
-        <is>
-          <t>Client conduct</t>
-        </is>
-      </c>
-      <c r="E179" s="10" t="inlineStr"/>
-    </row>
-    <row r="180">
-      <c r="A180" s="21" t="inlineStr"/>
-      <c r="B180" s="13" t="inlineStr"/>
-      <c r="C180" s="21" t="n">
+      <c r="D187" s="21" t="inlineStr">
+        <is>
+          <t>STR drafted</t>
+        </is>
+      </c>
+      <c r="E187" s="13" t="inlineStr"/>
+    </row>
+    <row r="188">
+      <c r="A188" s="18" t="inlineStr"/>
+      <c r="B188" s="10" t="inlineStr"/>
+      <c r="C188" s="18" t="n">
         <v>7</v>
       </c>
-      <c r="D180" s="21" t="inlineStr">
-        <is>
-          <t>Settlement</t>
-        </is>
-      </c>
-      <c r="E180" s="13" t="inlineStr"/>
-    </row>
-    <row r="181">
-      <c r="A181" s="18" t="inlineStr"/>
-      <c r="B181" s="10" t="inlineStr"/>
-      <c r="C181" s="18" t="n">
+      <c r="D188" s="18" t="inlineStr">
+        <is>
+          <t>Passed — not suspicious</t>
+        </is>
+      </c>
+      <c r="E188" s="10" t="inlineStr"/>
+    </row>
+    <row r="189">
+      <c r="A189" s="21" t="inlineStr"/>
+      <c r="B189" s="13" t="inlineStr"/>
+      <c r="C189" s="21" t="n">
         <v>8</v>
       </c>
-      <c r="D181" s="18" t="inlineStr">
-        <is>
-          <t>Financing</t>
-        </is>
-      </c>
-      <c r="E181" s="10" t="inlineStr"/>
-    </row>
-    <row r="182">
-      <c r="A182" s="21" t="inlineStr"/>
-      <c r="B182" s="13" t="inlineStr"/>
-      <c r="C182" s="21" t="n">
-        <v>9</v>
-      </c>
-      <c r="D182" s="21" t="inlineStr">
-        <is>
-          <t>Information misuse</t>
-        </is>
-      </c>
-      <c r="E182" s="13" t="inlineStr"/>
-    </row>
-    <row r="183">
-      <c r="A183" s="24" t="inlineStr">
-        <is>
-          <t>AUDIT_ACTION</t>
-        </is>
-      </c>
-      <c r="B183" s="25" t="inlineStr">
-        <is>
-          <t>FACT_ALERT_AUDIT.action</t>
-        </is>
-      </c>
-      <c r="C183" s="26" t="n">
+      <c r="D189" s="21" t="inlineStr">
+        <is>
+          <t>Opened for review</t>
+        </is>
+      </c>
+      <c r="E189" s="13" t="inlineStr"/>
+    </row>
+    <row r="190">
+      <c r="A190" s="24" t="inlineStr">
+        <is>
+          <t>CONTROL_LIST_TYPE</t>
+        </is>
+      </c>
+      <c r="B190" s="25" t="inlineStr">
+        <is>
+          <t>REF_CONTROL_LIST.list_type</t>
+        </is>
+      </c>
+      <c r="C190" s="26" t="n">
         <v>1</v>
       </c>
-      <c r="D183" s="26" t="inlineStr">
-        <is>
-          <t>Alert raised</t>
-        </is>
-      </c>
-      <c r="E183" s="25" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="184">
-      <c r="A184" s="21" t="inlineStr"/>
-      <c r="B184" s="13" t="inlineStr"/>
-      <c r="C184" s="21" t="n">
+      <c r="D190" s="26" t="inlineStr">
+        <is>
+          <t>RELATED_PARTY</t>
+        </is>
+      </c>
+      <c r="E190" s="25" t="inlineStr">
+        <is>
+          <t>All four are dated lists tested against a trade. Undated lists produce findings that are provably wrong.</t>
+        </is>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" s="21" t="inlineStr"/>
+      <c r="B191" s="13" t="inlineStr"/>
+      <c r="C191" s="21" t="n">
         <v>2</v>
       </c>
-      <c r="D184" s="21" t="inlineStr">
-        <is>
-          <t>Assigned</t>
-        </is>
-      </c>
-      <c r="E184" s="13" t="inlineStr"/>
-    </row>
-    <row r="185">
-      <c r="A185" s="18" t="inlineStr"/>
-      <c r="B185" s="10" t="inlineStr"/>
-      <c r="C185" s="18" t="n">
+      <c r="D191" s="21" t="inlineStr">
+        <is>
+          <t>RESTRICTED</t>
+        </is>
+      </c>
+      <c r="E191" s="13" t="inlineStr"/>
+    </row>
+    <row r="192">
+      <c r="A192" s="18" t="inlineStr"/>
+      <c r="B192" s="10" t="inlineStr"/>
+      <c r="C192" s="18" t="n">
         <v>3</v>
       </c>
-      <c r="D185" s="18" t="inlineStr">
-        <is>
-          <t>Escalated to Investigations</t>
-        </is>
-      </c>
-      <c r="E185" s="10" t="inlineStr"/>
-    </row>
-    <row r="186">
-      <c r="A186" s="21" t="inlineStr"/>
-      <c r="B186" s="13" t="inlineStr"/>
-      <c r="C186" s="21" t="n">
+      <c r="D192" s="18" t="inlineStr">
+        <is>
+          <t>WALL_CROSSING</t>
+        </is>
+      </c>
+      <c r="E192" s="10" t="inlineStr"/>
+    </row>
+    <row r="193">
+      <c r="A193" s="21" t="inlineStr"/>
+      <c r="B193" s="13" t="inlineStr"/>
+      <c r="C193" s="21" t="n">
         <v>4</v>
       </c>
-      <c r="D186" s="21" t="inlineStr">
-        <is>
-          <t>Case opened</t>
-        </is>
-      </c>
-      <c r="E186" s="13" t="inlineStr"/>
-    </row>
-    <row r="187">
-      <c r="A187" s="18" t="inlineStr"/>
-      <c r="B187" s="10" t="inlineStr"/>
-      <c r="C187" s="18" t="n">
-        <v>5</v>
-      </c>
-      <c r="D187" s="18" t="inlineStr">
-        <is>
-          <t>Tagged suspicious</t>
-        </is>
-      </c>
-      <c r="E187" s="10" t="inlineStr"/>
-    </row>
-    <row r="188">
-      <c r="A188" s="21" t="inlineStr"/>
-      <c r="B188" s="13" t="inlineStr"/>
-      <c r="C188" s="21" t="n">
-        <v>6</v>
-      </c>
-      <c r="D188" s="21" t="inlineStr">
-        <is>
-          <t>STR drafted</t>
-        </is>
-      </c>
-      <c r="E188" s="13" t="inlineStr"/>
-    </row>
-    <row r="189">
-      <c r="A189" s="18" t="inlineStr"/>
-      <c r="B189" s="10" t="inlineStr"/>
-      <c r="C189" s="18" t="n">
-        <v>7</v>
-      </c>
-      <c r="D189" s="18" t="inlineStr">
-        <is>
-          <t>Passed — not suspicious</t>
-        </is>
-      </c>
-      <c r="E189" s="10" t="inlineStr"/>
-    </row>
-    <row r="190">
-      <c r="A190" s="21" t="inlineStr"/>
-      <c r="B190" s="13" t="inlineStr"/>
-      <c r="C190" s="21" t="n">
-        <v>8</v>
-      </c>
-      <c r="D190" s="21" t="inlineStr">
-        <is>
-          <t>Opened for review</t>
-        </is>
-      </c>
-      <c r="E190" s="13" t="inlineStr"/>
-    </row>
-    <row r="191">
-      <c r="A191" s="24" t="inlineStr">
-        <is>
-          <t>CONTROL_LIST_TYPE</t>
-        </is>
-      </c>
-      <c r="B191" s="25" t="inlineStr">
-        <is>
-          <t>REF_CONTROL_LIST.list_type</t>
-        </is>
-      </c>
-      <c r="C191" s="26" t="n">
-        <v>1</v>
-      </c>
-      <c r="D191" s="26" t="inlineStr">
-        <is>
-          <t>RELATED_PARTY</t>
-        </is>
-      </c>
-      <c r="E191" s="25" t="inlineStr">
-        <is>
-          <t>All four are dated lists tested against a trade. Undated lists produce findings that are provably wrong.</t>
-        </is>
-      </c>
-    </row>
-    <row r="192">
-      <c r="A192" s="21" t="inlineStr"/>
-      <c r="B192" s="13" t="inlineStr"/>
-      <c r="C192" s="21" t="n">
-        <v>2</v>
-      </c>
-      <c r="D192" s="21" t="inlineStr">
-        <is>
-          <t>RESTRICTED</t>
-        </is>
-      </c>
-      <c r="E192" s="13" t="inlineStr"/>
-    </row>
-    <row r="193">
-      <c r="A193" s="18" t="inlineStr"/>
-      <c r="B193" s="10" t="inlineStr"/>
-      <c r="C193" s="18" t="n">
-        <v>3</v>
-      </c>
-      <c r="D193" s="18" t="inlineStr">
-        <is>
-          <t>WALL_CROSSING</t>
-        </is>
-      </c>
-      <c r="E193" s="10" t="inlineStr"/>
-    </row>
-    <row r="194">
-      <c r="A194" s="21" t="inlineStr"/>
-      <c r="B194" s="13" t="inlineStr"/>
-      <c r="C194" s="21" t="n">
-        <v>4</v>
-      </c>
-      <c r="D194" s="21" t="inlineStr">
+      <c r="D193" s="21" t="inlineStr">
         <is>
           <t>HIGH_RISK_JURISDICTION</t>
         </is>
       </c>
-      <c r="E194" s="13" t="inlineStr"/>
-    </row>
+      <c r="E193" s="13" t="inlineStr"/>
+    </row>
+    <row r="194"/>
+    <row r="195"/>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -17840,7 +17803,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4" ht="30" customHeight="1">
       <c r="A4" s="9" t="inlineStr">
         <is>
@@ -19095,7 +19057,6 @@
         </is>
       </c>
     </row>
-    <row r="26"/>
     <row r="27">
       <c r="A27" s="30" t="inlineStr">
         <is>
@@ -19199,7 +19160,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4" ht="30" customHeight="1">
       <c r="A4" s="9" t="inlineStr">
         <is>
@@ -21455,11 +21415,10 @@
     <row r="3">
       <c r="A3" s="17" t="inlineStr">
         <is>
-          <t>Source: Trade capture (booking systems), enriched with market data and FX rates   |   Refresh: Intraday, at least hourly; full reconciliation end of day   |   Volume: ~59k rows per rolling year in the prototype; size for your real daily deal count x 400 days   |   Priority: 1 — Blocking</t>
-        </is>
-      </c>
-    </row>
-    <row r="4"/>
+          <t>Source: Trade capture (booking systems), enriched with market data and FX rates   |   Refresh: Intraday, at least hourly; full reconciliation end of day   |   Volume: ~60k rows per rolling year in the prototype; size for your real daily deal count x 400 days   |   Priority: 1 — Blocking</t>
+        </is>
+      </c>
+    </row>
     <row r="5" ht="30" customHeight="1">
       <c r="A5" s="9" t="inlineStr">
         <is>
@@ -24193,7 +24152,7 @@
       </c>
       <c r="H54" s="10" t="inlineStr">
         <is>
-          <t>0 .. 95 observed in the prototype; 0 for internal transfers</t>
+          <t>0 .. 150 observed in the prototype, 99% of tickets under 12; 0 for internal transfers</t>
         </is>
       </c>
       <c r="I54" s="10" t="inlineStr">
@@ -24248,7 +24207,7 @@
       </c>
       <c r="H55" s="13" t="inlineStr">
         <is>
-          <t>-8 .. +131 observed; roughly one ticket in ten negative</t>
+          <t>-261 .. +341 observed, 99% of tickets between -1 and +15; about 12% of tickets negative</t>
         </is>
       </c>
       <c r="I55" s="13" t="inlineStr">
@@ -24474,7 +24433,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4" ht="30" customHeight="1">
       <c r="A4" s="9" t="inlineStr">
         <is>
@@ -26937,7 +26895,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4">
       <c r="A4" s="42" t="inlineStr">
         <is>
@@ -33781,7 +33738,6 @@
       <c r="BM63" s="46" t="n"/>
       <c r="BN63" s="46" t="n"/>
     </row>
-    <row r="64"/>
     <row r="65">
       <c r="A65" s="47" t="inlineStr">
         <is>
@@ -34014,7 +33970,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4" ht="30" customHeight="1">
       <c r="A4" s="9" t="inlineStr">
         <is>
@@ -35524,7 +35479,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4" ht="30" customHeight="1">
       <c r="A4" s="9" t="inlineStr">
         <is>
@@ -36347,7 +36301,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4" ht="30" customHeight="1">
       <c r="A4" s="9" t="inlineStr">
         <is>
@@ -36774,11 +36727,10 @@
     <row r="3">
       <c r="A3" s="17" t="inlineStr">
         <is>
-          <t>Source: Trade capture audit log   |   Refresh: Intraday, with the trade feed   |   Volume: 7.1% of deals carry at least one amendment; 0.7% are cancelled   |   Priority: 1 — Blocking</t>
-        </is>
-      </c>
-    </row>
-    <row r="4"/>
+          <t>Source: Trade capture audit log   |   Refresh: Intraday, with the trade feed   |   Volume: 7.0% of deals carry at least one amendment; 0.7% are cancelled   |   Priority: 1 — Blocking</t>
+        </is>
+      </c>
+    </row>
     <row r="5" ht="30" customHeight="1">
       <c r="A5" s="9" t="inlineStr">
         <is>
@@ -37383,7 +37335,6 @@
         </is>
       </c>
     </row>
-    <row r="4"/>
     <row r="5" ht="30" customHeight="1">
       <c r="A5" s="9" t="inlineStr">
         <is>
@@ -38208,7 +38159,6 @@
         </is>
       </c>
     </row>
-    <row r="4"/>
     <row r="5" ht="30" customHeight="1">
       <c r="A5" s="9" t="inlineStr">
         <is>
@@ -38813,7 +38763,6 @@
         </is>
       </c>
     </row>
-    <row r="4"/>
     <row r="5" ht="30" customHeight="1">
       <c r="A5" s="9" t="inlineStr">
         <is>
@@ -39473,7 +39422,6 @@
         </is>
       </c>
     </row>
-    <row r="4"/>
     <row r="5" ht="30" customHeight="1">
       <c r="A5" s="9" t="inlineStr">
         <is>
@@ -39968,7 +39916,6 @@
         </is>
       </c>
     </row>
-    <row r="4"/>
     <row r="5" ht="30" customHeight="1">
       <c r="A5" s="9" t="inlineStr">
         <is>

--- a/Trade-Surveillance-Data-Schema.xlsx
+++ b/Trade-Surveillance-Data-Schema.xlsx
@@ -17759,8 +17759,6 @@
       </c>
       <c r="E193" s="13" t="inlineStr"/>
     </row>
-    <row r="194"/>
-    <row r="195"/>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -33966,7 +33964,7 @@
     <row r="2" ht="14" customHeight="1">
       <c r="A2" s="42" t="inlineStr">
         <is>
-          <t>All 33 panels across the 8 dashboard tabs. If a panel is not needed, the tables in its row may still be required by others — check '01 Table Index' before dropping anything. The thirteen Trade Activity panels are drawn in a measure the reader chooses — deals and notional, or P&amp;L and margin — so each one has two readings of the same cut and needs the revenue fields as well as the volume ones.</t>
+          <t>All 33 panels across the 8 dashboard tabs. If a panel is not needed, the tables in its row may still be required by others — check '01 Table Index' before dropping anything. The thirteen Trade Activity panels are drawn in a measure the reader chooses — deals and notional, or P&amp;L and margin — so each one has two readings of the same cut and needs the revenue fields as well as the volume ones. Tables page and long card grids load in batches; every count on a panel describes the full filtered set, never only the rows on screen.</t>
         </is>
       </c>
     </row>
@@ -34949,7 +34947,7 @@
       </c>
       <c r="C27" s="13" t="inlineStr">
         <is>
-          <t>Ranked bar, selectable</t>
+          <t>Small multiples, one per trader, loads in batches</t>
         </is>
       </c>
       <c r="D27" s="13" t="inlineStr">
@@ -34974,7 +34972,7 @@
       </c>
       <c r="H27" s="13" t="inlineStr">
         <is>
-          <t>Selecting a bar re-scopes every panel above it, so it must share the trader key exactly.</t>
+          <t>Clicking a trader's name re-scopes every panel on the page, so it must share the trader key exactly. Loads 24 traders at a time, the next batch as the reader scrolls.</t>
         </is>
       </c>
     </row>
@@ -35033,7 +35031,7 @@
       </c>
       <c r="C29" s="13" t="inlineStr">
         <is>
-          <t>Table with drill-down</t>
+          <t>Table with drill-down, paged (25 a page)</t>
         </is>
       </c>
       <c r="D29" s="13" t="inlineStr">
@@ -35058,7 +35056,7 @@
       </c>
       <c r="H29" s="13" t="inlineStr">
         <is>
-          <t>Clicking an alert opens the cited deals and the evidence lines. All four tables are needed for the drawer.</t>
+          <t>Clicking an alert opens the cited deals and the evidence lines. All four tables are needed for the drawer. Paged after the full set is filtered and sorted, so the pager's total is the count of every matching row. At production volume the query behind it must return that total and accept a page offset and size, applying the same filter and sort — otherwise the total will disagree with the count that opened it. The heatmap-cell count and the queue's total must match exactly.</t>
         </is>
       </c>
     </row>
@@ -35075,7 +35073,7 @@
       </c>
       <c r="C30" s="10" t="inlineStr">
         <is>
-          <t>Card list</t>
+          <t>Card list, loads in batches</t>
         </is>
       </c>
       <c r="D30" s="10" t="inlineStr">
@@ -35100,7 +35098,7 @@
       </c>
       <c r="H30" s="10" t="inlineStr">
         <is>
-          <t>The data-requirements section of each card is generated from the rule-to-element mapping, not written by hand.</t>
+          <t>The data-requirements section of each card is generated from the rule-to-element mapping, not written by hand. Loads 24 rules at a time, the next batch as the reader scrolls, with a Show all button.</t>
         </is>
       </c>
     </row>
@@ -35117,7 +35115,7 @@
       </c>
       <c r="C31" s="13" t="inlineStr">
         <is>
-          <t>Table</t>
+          <t>Table, paged (50 a page)</t>
         </is>
       </c>
       <c r="D31" s="13" t="inlineStr">
@@ -35142,7 +35140,7 @@
       </c>
       <c r="H31" s="13" t="inlineStr">
         <is>
-          <t>The lowest-level view. Every column here has to be present on FACT_TRADE or joinable from it in one hop.</t>
+          <t>The lowest-level view. Every column here has to be present on FACT_TRADE or joinable from it in one hop. Paged after the full set is filtered and sorted, so the pager's total is the count of every matching row. At production volume the query behind it must return that total and accept a page offset and size, applying the same filter and sort — otherwise the total will disagree with the count that opened it.</t>
         </is>
       </c>
     </row>
@@ -35226,7 +35224,7 @@
       </c>
       <c r="H33" s="13" t="inlineStr">
         <is>
-          <t>Same panel and same source as the Overview heatmap, transposed.</t>
+          <t>Same panel and same source as the Overview heatmap, transposed. Shows the 14 traders with the most alerts, and says so.</t>
         </is>
       </c>
     </row>
@@ -35285,7 +35283,7 @@
       </c>
       <c r="C35" s="13" t="inlineStr">
         <is>
-          <t>Ranked bar</t>
+          <t>Ranked card grid, loads in batches</t>
         </is>
       </c>
       <c r="D35" s="13" t="inlineStr">
@@ -35310,7 +35308,7 @@
       </c>
       <c r="H35" s="13" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Ranked over every trader in scope before it is cut into batches; loads 25 traders at a time, the next batch as the reader scrolls.</t>
         </is>
       </c>
     </row>
@@ -35411,7 +35409,7 @@
       </c>
       <c r="C38" s="10" t="inlineStr">
         <is>
-          <t>Table</t>
+          <t>Table, paged (25 a page)</t>
         </is>
       </c>
       <c r="D38" s="10" t="inlineStr">
@@ -35436,7 +35434,7 @@
       </c>
       <c r="H38" s="10" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Paged after the full set is filtered and sorted, so the pager's total is the count of every matching row. At production volume the query behind it must return that total and accept a page offset and size, applying the same filter and sort — otherwise the total will disagree with the count that opened it.</t>
         </is>
       </c>
     </row>
